--- a/test_case/CAB_System_TestCases.xlsx
+++ b/test_case/CAB_System_TestCases.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vthai/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vthai/Documents/LTHDV/BTTH/23674231_TranVanThai_Cabsystem/test_case/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F47E1C0-69E4-5445-8413-9D70BF4BC8CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EF805A8-7E5A-8B47-8297-CA3C052A9696}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="18380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,27 +40,24 @@
     <sheet name="UC25" sheetId="25" r:id="rId25"/>
     <sheet name="UC26" sheetId="26" r:id="rId26"/>
     <sheet name="UC27" sheetId="27" r:id="rId27"/>
-    <sheet name="UC28" sheetId="28" r:id="rId28"/>
-    <sheet name="UC29" sheetId="29" r:id="rId29"/>
-    <sheet name="UC30" sheetId="30" r:id="rId30"/>
-    <sheet name="UC31" sheetId="31" r:id="rId31"/>
-    <sheet name="UC32" sheetId="32" r:id="rId32"/>
-    <sheet name="UC33" sheetId="33" r:id="rId33"/>
-    <sheet name="UC34" sheetId="34" r:id="rId34"/>
-    <sheet name="UC35" sheetId="35" r:id="rId35"/>
-    <sheet name="UC36" sheetId="36" r:id="rId36"/>
-    <sheet name="UC37" sheetId="37" r:id="rId37"/>
-    <sheet name="UC38" sheetId="38" r:id="rId38"/>
-    <sheet name="UC39" sheetId="39" r:id="rId39"/>
-    <sheet name="UC40" sheetId="40" r:id="rId40"/>
-    <sheet name="UC41" sheetId="41" r:id="rId41"/>
+    <sheet name="UC30" sheetId="28" r:id="rId28"/>
+    <sheet name="UC31" sheetId="29" r:id="rId29"/>
+    <sheet name="UC32" sheetId="30" r:id="rId30"/>
+    <sheet name="UC33" sheetId="31" r:id="rId31"/>
+    <sheet name="UC34" sheetId="32" r:id="rId32"/>
+    <sheet name="UC35" sheetId="33" r:id="rId33"/>
+    <sheet name="UC36" sheetId="34" r:id="rId34"/>
+    <sheet name="UC37" sheetId="35" r:id="rId35"/>
+    <sheet name="UC39" sheetId="36" r:id="rId36"/>
+    <sheet name="UC40" sheetId="37" r:id="rId37"/>
+    <sheet name="UC41" sheetId="38" r:id="rId38"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2089" uniqueCount="1473">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1974" uniqueCount="1402">
   <si>
     <t>UC01 - Dang ky</t>
   </si>
@@ -2885,1417 +2882,1204 @@
     <t>User chua co Notification</t>
   </si>
   <si>
-    <t>UC28 - Danh dau Notification da doc</t>
-  </si>
-  <si>
-    <t>TC_FR74_POS</t>
-  </si>
-  <si>
-    <t>[Positive] Danh dau Notification da doc (FR74)</t>
-  </si>
-  <si>
-    <t>[Positive] Danh dau Notification da doc</t>
-  </si>
-  <si>
-    <t>Notification thuoc user; isRead=false.</t>
-  </si>
-  <si>
-    <t>1.Mo Notification 2.Danh dau da doc</t>
-  </si>
-  <si>
-    <t>Notification unread</t>
-  </si>
-  <si>
-    <t>isRead=true va readAt duoc luu.</t>
-  </si>
-  <si>
-    <t>TC_FR74_REPEAT</t>
-  </si>
-  <si>
-    <t>[Positive] Danh dau Notification da doc da doc (FR74)</t>
-  </si>
-  <si>
-    <t>[Positive] Danh dau Notification da doc da doc</t>
-  </si>
-  <si>
-    <t>Notification isRead=true.</t>
-  </si>
-  <si>
-    <t>1.Gui request read</t>
-  </si>
-  <si>
-    <t>Notification da doc</t>
-  </si>
-  <si>
-    <t>Trang thai van nhat quan; khong tao du lieu doc moi bat hop ly.</t>
-  </si>
-  <si>
-    <t>UC29 - Xu ly Incident</t>
-  </si>
-  <si>
-    <t>TC_FR81_82_POS</t>
-  </si>
-  <si>
-    <t>[Positive] Tao va xem Incident (FR81,82)</t>
-  </si>
-  <si>
-    <t>[Positive] Tao va xem Incident</t>
-  </si>
-  <si>
-    <t>1.Tao Incident 2.Mo danh sach/chi tiet</t>
-  </si>
-  <si>
-    <t>Incident hop le; trip co the null</t>
-  </si>
-  <si>
-    <t>Incident duoc CREATE va xem duoc; Incident co the khong gan Trip.</t>
-  </si>
-  <si>
-    <t>TC_FR83_84_85_POS</t>
-  </si>
-  <si>
-    <t>[Positive] Cap nhat Incident va ghi resolution (FR83,84,85)</t>
-  </si>
-  <si>
-    <t>[Positive] Cap nhat Incident va ghi resolution</t>
-  </si>
-  <si>
-    <t>Incident ton tai; Staff co permission.</t>
-  </si>
-  <si>
-    <t>1.Sua type/description 2.Doi status 3.Nhap resolution</t>
-  </si>
-  <si>
-    <t>Incident status; resolution</t>
-  </si>
-  <si>
-    <t>Incident duoc UPDATE dung thong tin va resolution.</t>
-  </si>
-  <si>
-    <t>TC_FR86_87_POS</t>
-  </si>
-  <si>
-    <t>[Positive] Dong Incident va luu thoi gian xu ly (FR86,87)</t>
-  </si>
-  <si>
-    <t>[Positive] Dong Incident va luu thoi gian xu ly</t>
-  </si>
-  <si>
-    <t>Incident da resolved theo flow.</t>
-  </si>
-  <si>
-    <t>1.Dong Incident 2.Kiem tra</t>
-  </si>
-  <si>
-    <t>Status CLOSED</t>
-  </si>
-  <si>
-    <t>Incident=CLOSED va thoi gian xu ly/resolvedAt duoc luu theo flow.</t>
-  </si>
-  <si>
-    <t>TC_FR95_AUTH</t>
-  </si>
-  <si>
-    <t>[Negative] Staff khong co permission khong duoc xu ly Incident (FR95)</t>
-  </si>
-  <si>
-    <t>[Negative] Staff khong co permission khong duoc xu ly Incident</t>
+    <t>UC30 - Quan ly Customer</t>
+  </si>
+  <si>
+    <t>TC_FR88_POS</t>
+  </si>
+  <si>
+    <t>[Positive] Operations xem Customer (FR88)</t>
+  </si>
+  <si>
+    <t>[Positive] Operations xem Customer</t>
+  </si>
+  <si>
+    <t>1.Mo Customers</t>
+  </si>
+  <si>
+    <t>Customer data</t>
+  </si>
+  <si>
+    <t>He thong hien thi Customer trong pham vi quyen.</t>
+  </si>
+  <si>
+    <t>TC_FR88_SEARCH</t>
+  </si>
+  <si>
+    <t>[Positive] Tim kiem Customer (FR88)</t>
+  </si>
+  <si>
+    <t>[Positive] Tim kiem Customer</t>
+  </si>
+  <si>
+    <t>Co nhieu Customer.</t>
+  </si>
+  <si>
+    <t>1.Nhap dieu kien tim kiem</t>
+  </si>
+  <si>
+    <t>Tu khoa hop le</t>
+  </si>
+  <si>
+    <t>He thong tra dung Customer phu hop.</t>
+  </si>
+  <si>
+    <t>TC_FR88_FILTER</t>
+  </si>
+  <si>
+    <t>[Positive] Loc Customer (FR88)</t>
+  </si>
+  <si>
+    <t>[Positive] Loc Customer</t>
+  </si>
+  <si>
+    <t>Co du lieu Customer.</t>
+  </si>
+  <si>
+    <t>1.Chon bo loc</t>
+  </si>
+  <si>
+    <t>Bo loc hop le</t>
+  </si>
+  <si>
+    <t>He thong tra dung tap Customer phu hop.</t>
+  </si>
+  <si>
+    <t>TC_FR88_DETAIL</t>
+  </si>
+  <si>
+    <t>[Positive] Xem chi tiet Customer (FR88)</t>
+  </si>
+  <si>
+    <t>[Positive] Xem chi tiet Customer</t>
+  </si>
+  <si>
+    <t>1.Chon Customer</t>
+  </si>
+  <si>
+    <t>customerId hop le</t>
+  </si>
+  <si>
+    <t>He thong hien thi chi tiet Customer.</t>
+  </si>
+  <si>
+    <t>TC_FR88_DENY</t>
+  </si>
+  <si>
+    <t>[Negative] Khong truy cap Customer khi thieu permission (FR88)</t>
+  </si>
+  <si>
+    <t>[Negative] Khong truy cap Customer khi thieu permission</t>
   </si>
   <si>
     <t>Staff khong co permission.</t>
   </si>
   <si>
-    <t>1.Gui create/update Incident</t>
-  </si>
-  <si>
-    <t>He thong tra 403 va khong thay doi du lieu.</t>
-  </si>
-  <si>
-    <t>TC_FR95_AUDIT</t>
-  </si>
-  <si>
-    <t>[Positive] Xu ly Incident ghi AuditLog (FR95)</t>
-  </si>
-  <si>
-    <t>[Positive] Xu ly Incident ghi AuditLog</t>
-  </si>
-  <si>
-    <t>1.Cap nhat Incident 2.Kiem tra AuditLog</t>
-  </si>
-  <si>
-    <t>Thao tac xu ly Incident</t>
-  </si>
-  <si>
-    <t>AuditLog duoc ghi cho thao tac quan tri/xu ly quan trong.</t>
-  </si>
-  <si>
-    <t>TC_LOG_UNEXPECTED</t>
-  </si>
-  <si>
-    <t>[Exception] Ghi log unexpected exception (FR95)</t>
-  </si>
-  <si>
-    <t>[Exception] Ghi log unexpected exception</t>
-  </si>
-  <si>
-    <t>Staff xu ly Incident; phat sinh loi ngoai du kien.</t>
-  </si>
-  <si>
-    <t>1.Thuc hien thao tac 2.Phat sinh exception 3.Kiem tra log</t>
-  </si>
-  <si>
-    <t>Unexpected exception</t>
-  </si>
-  <si>
-    <t>Unexpected exception duoc log; thong tin nhay cam khong bi ghi vao log.</t>
-  </si>
-  <si>
-    <t>TC_FR82_EMPTY</t>
-  </si>
-  <si>
-    <t>[Exception] Operations xem danh sach Incident khi chua co Incident nao (FR82)</t>
-  </si>
-  <si>
-    <t>[Exception] Operations xem danh sach Incident khi chua co Incident nao</t>
-  </si>
-  <si>
-    <t>Operations Staff dang nhap co permission; he thong chua co Incident nao.</t>
-  </si>
-  <si>
-    <t>1.Goi API xem danh sach Incident</t>
-  </si>
-  <si>
-    <t>Chua co Incident nao trong he thong</t>
+    <t>TC_FR88_NORESULT</t>
+  </si>
+  <si>
+    <t>[Exception] Tim kiem/loc Customer khong khop ket qua nao (FR88)</t>
+  </si>
+  <si>
+    <t>[Exception] Tim kiem/loc Customer khong khop ket qua nao</t>
+  </si>
+  <si>
+    <t>Operations Staff co permission xem Customer.</t>
+  </si>
+  <si>
+    <t>1.Nhap tu khoa tim kiem/dieu kien loc khong khop Customer nao 2.Xem ket qua</t>
+  </si>
+  <si>
+    <t>Tu khoa/dieu kien khong khop du lieu nao</t>
+  </si>
+  <si>
+    <t>He thong tra ve danh sach rong; khong loi; khong tra nham du lieu khac.</t>
+  </si>
+  <si>
+    <t>UC31 - Quan ly Driver</t>
+  </si>
+  <si>
+    <t>TC_FR89_POS</t>
+  </si>
+  <si>
+    <t>[Positive] Operations xem Driver va trang thai (FR89,93)</t>
+  </si>
+  <si>
+    <t>[Positive] Operations xem Driver va trang thai</t>
+  </si>
+  <si>
+    <t>1.Mo Drivers 2.Xem status</t>
+  </si>
+  <si>
+    <t>Driver data</t>
+  </si>
+  <si>
+    <t>He thong hien thi Driver va status dung.</t>
+  </si>
+  <si>
+    <t>TC_FR89_SEARCH</t>
+  </si>
+  <si>
+    <t>[Positive] Tim kiem Driver (FR89)</t>
+  </si>
+  <si>
+    <t>[Positive] Tim kiem Driver</t>
+  </si>
+  <si>
+    <t>Co nhieu Driver.</t>
+  </si>
+  <si>
+    <t>1.Nhap tu khoa</t>
+  </si>
+  <si>
+    <t>He thong tra dung Driver.</t>
+  </si>
+  <si>
+    <t>TC_FR89_FILTER</t>
+  </si>
+  <si>
+    <t>[Positive] Loc Driver (FR89)</t>
+  </si>
+  <si>
+    <t>[Positive] Loc Driver</t>
+  </si>
+  <si>
+    <t>Co du lieu Driver.</t>
+  </si>
+  <si>
+    <t>TC_FR89_DETAIL</t>
+  </si>
+  <si>
+    <t>[Positive] Xem chi tiet Driver (FR89)</t>
+  </si>
+  <si>
+    <t>[Positive] Xem chi tiet Driver</t>
+  </si>
+  <si>
+    <t>1.Chon Driver</t>
+  </si>
+  <si>
+    <t>driverId</t>
+  </si>
+  <si>
+    <t>He thong hien thi chi tiet Driver.</t>
+  </si>
+  <si>
+    <t>TC_FR89_DENY</t>
+  </si>
+  <si>
+    <t>[Negative] Thieu permission khi xem Driver (FR89)</t>
+  </si>
+  <si>
+    <t>[Negative] Thieu permission khi xem Driver</t>
+  </si>
+  <si>
+    <t>1.Mo Drivers</t>
+  </si>
+  <si>
+    <t>Khong permission</t>
+  </si>
+  <si>
+    <t>TC_FR89_NORESULT</t>
+  </si>
+  <si>
+    <t>[Exception] Tim kiem/loc Driver khong khop ket qua nao (FR89)</t>
+  </si>
+  <si>
+    <t>[Exception] Tim kiem/loc Driver khong khop ket qua nao</t>
+  </si>
+  <si>
+    <t>Operations Staff co permission xem Driver.</t>
+  </si>
+  <si>
+    <t>1.Nhap tu khoa tim kiem/dieu kien loc khong khop Driver nao 2.Xem ket qua</t>
+  </si>
+  <si>
+    <t>UC32 - Quan ly Vehicle</t>
+  </si>
+  <si>
+    <t>TC_FR90_POS</t>
+  </si>
+  <si>
+    <t>[Positive] Operations xem va quan ly Vehicle (FR90)</t>
+  </si>
+  <si>
+    <t>[Positive] Operations xem va quan ly Vehicle</t>
+  </si>
+  <si>
+    <t>1.Mo Vehicles 2.Xem detail</t>
+  </si>
+  <si>
+    <t>Vehicle data</t>
+  </si>
+  <si>
+    <t>He thong cho xem Vehicle trong pham vi.</t>
+  </si>
+  <si>
+    <t>TC_FR90_SEARCH</t>
+  </si>
+  <si>
+    <t>[Positive] Tim kiem Vehicle (FR90)</t>
+  </si>
+  <si>
+    <t>[Positive] Tim kiem Vehicle</t>
+  </si>
+  <si>
+    <t>Co nhieu Vehicle.</t>
+  </si>
+  <si>
+    <t>Tu khoa</t>
+  </si>
+  <si>
+    <t>He thong tra dung Vehicle.</t>
+  </si>
+  <si>
+    <t>TC_FR90_FILTER</t>
+  </si>
+  <si>
+    <t>[Positive] Loc Vehicle (FR90)</t>
+  </si>
+  <si>
+    <t>[Positive] Loc Vehicle</t>
+  </si>
+  <si>
+    <t>Co Vehicle.</t>
+  </si>
+  <si>
+    <t>1.Chon filter</t>
+  </si>
+  <si>
+    <t>Filter hop le</t>
+  </si>
+  <si>
+    <t>TC_FR90_STATUS</t>
+  </si>
+  <si>
+    <t>[Positive] Cap nhat trang thai Vehicle (FR90)</t>
+  </si>
+  <si>
+    <t>[Positive] Cap nhat trang thai Vehicle</t>
+  </si>
+  <si>
+    <t>Staff co permission; Vehicle ton tai.</t>
+  </si>
+  <si>
+    <t>1.Chon Vehicle 2.Update status</t>
+  </si>
+  <si>
+    <t>ACTIVE/INACTIVE</t>
+  </si>
+  <si>
+    <t>Trang thai Vehicle duoc UPDATE theo quyen.</t>
+  </si>
+  <si>
+    <t>TC_FR90_DENY</t>
+  </si>
+  <si>
+    <t>[Negative] Thieu permission khi quan ly Vehicle (FR90)</t>
+  </si>
+  <si>
+    <t>[Negative] Thieu permission khi quan ly Vehicle</t>
+  </si>
+  <si>
+    <t>1.Update Vehicle</t>
+  </si>
+  <si>
+    <t>TC_FR90_NORESULT</t>
+  </si>
+  <si>
+    <t>[Exception] Tim kiem/loc Vehicle khong khop ket qua nao (FR90)</t>
+  </si>
+  <si>
+    <t>[Exception] Tim kiem/loc Vehicle khong khop ket qua nao</t>
+  </si>
+  <si>
+    <t>Operations Staff co permission xem Vehicle.</t>
+  </si>
+  <si>
+    <t>1.Nhap tu khoa tim kiem/dieu kien loc khong khop Vehicle nao 2.Xem ket qua</t>
+  </si>
+  <si>
+    <t>UC33 - Theo doi Trip</t>
+  </si>
+  <si>
+    <t>TC_FR91_POS</t>
+  </si>
+  <si>
+    <t>[Positive] Xem danh sach Trip (FR91)</t>
+  </si>
+  <si>
+    <t>[Positive] Xem danh sach Trip</t>
+  </si>
+  <si>
+    <t>1.Mo Trips</t>
+  </si>
+  <si>
+    <t>Trip data</t>
+  </si>
+  <si>
+    <t>He thong hien thi danh sach Trip trong pham vi.</t>
+  </si>
+  <si>
+    <t>TC_FR92_POS</t>
+  </si>
+  <si>
+    <t>[Positive] Xem chi tiet Trip (FR92)</t>
+  </si>
+  <si>
+    <t>[Positive] Xem chi tiet Trip</t>
+  </si>
+  <si>
+    <t>1.Chon Trip</t>
+  </si>
+  <si>
+    <t>tripId</t>
+  </si>
+  <si>
+    <t>He thong hien thi Trip ID, Customer, Driver, Vehicle, pickup, destination, status, fare, createdAt.</t>
+  </si>
+  <si>
+    <t>TC_FR93_POS</t>
+  </si>
+  <si>
+    <t>[Positive] Theo doi Driver (FR93)</t>
+  </si>
+  <si>
+    <t>[Positive] Theo doi Driver</t>
+  </si>
+  <si>
+    <t>1.Mo theo doi Driver</t>
+  </si>
+  <si>
+    <t>Driver current status/location</t>
+  </si>
+  <si>
+    <t>He thong hien thi thong tin theo doi Driver trong pham vi.</t>
+  </si>
+  <si>
+    <t>TC_FR91_PAG</t>
+  </si>
+  <si>
+    <t>[Positive] Danh sach lon co pagination (FR91)</t>
+  </si>
+  <si>
+    <t>[Positive] Danh sach lon co pagination</t>
+  </si>
+  <si>
+    <t>Danh sach Trip lon.</t>
+  </si>
+  <si>
+    <t>1.Mo danh sach 2.Chuyen trang</t>
+  </si>
+  <si>
+    <t>Nhieu ban ghi</t>
+  </si>
+  <si>
+    <t>He thong phan trang va khong can load tat ca record vao mot trang (NFR10).</t>
+  </si>
+  <si>
+    <t>TC_FR91_DENY</t>
+  </si>
+  <si>
+    <t>[Negative] Thieu permission khi theo doi Trip (FR91,92,93)</t>
+  </si>
+  <si>
+    <t>[Negative] Thieu permission khi theo doi Trip</t>
+  </si>
+  <si>
+    <t>TC_FR55_POS</t>
+  </si>
+  <si>
+    <t>[Positive] Customer xem vi tri Driver (FR55)</t>
+  </si>
+  <si>
+    <t>[Positive] Customer xem vi tri Driver</t>
+  </si>
+  <si>
+    <t>Customer dang co Trip va Driver co current location.</t>
+  </si>
+  <si>
+    <t>1.Mo tracking Trip</t>
+  </si>
+  <si>
+    <t>Driver.currentLatitude/currentLongitude</t>
+  </si>
+  <si>
+    <t>He thong hien thi vi tri hien tai cua Driver cho Customer theo quyen.</t>
+  </si>
+  <si>
+    <t>TC_FR56_POS</t>
+  </si>
+  <si>
+    <t>[Positive] Operations Staff xem vi tri Driver (FR56)</t>
+  </si>
+  <si>
+    <t>[Positive] Operations Staff xem vi tri Driver</t>
+  </si>
+  <si>
+    <t>Staff co permission; Driver co current location.</t>
+  </si>
+  <si>
+    <t>1.Mo tracking Driver</t>
+  </si>
+  <si>
+    <t>Driver location</t>
+  </si>
+  <si>
+    <t>He thong hien thi vi tri hien tai cua Driver cho Staff.</t>
+  </si>
+  <si>
+    <t>TC_NFR08_RESPONSE</t>
+  </si>
+  <si>
+    <t>[Positive] Chuc nang thong thuong phan hoi phu hop moi truong MVP (FR91,92,93)</t>
+  </si>
+  <si>
+    <t>[Positive] Chuc nang thong thuong phan hoi phu hop moi truong MVP</t>
+  </si>
+  <si>
+    <t>He thong o moi truong MVP.</t>
+  </si>
+  <si>
+    <t>1.Thuc hien thao tac thong thuong 2.Do thoi gian phan hoi</t>
+  </si>
+  <si>
+    <t>Request thong thuong</t>
+  </si>
+  <si>
+    <t>Thoi gian phan hoi dap ung benchmark phu hop moi truong MVP; khong co timeout bat thuong (NFR08).</t>
+  </si>
+  <si>
+    <t>TC_FR91_EMPTY</t>
+  </si>
+  <si>
+    <t>[Exception] Operations xem danh sach Trip khi he thong chua co Trip nao (FR91)</t>
+  </si>
+  <si>
+    <t>[Exception] Operations xem danh sach Trip khi he thong chua co Trip nao</t>
+  </si>
+  <si>
+    <t>Operations Staff co permission; he thong chua co Trip nao.</t>
+  </si>
+  <si>
+    <t>1.Goi API xem danh sach Trip</t>
+  </si>
+  <si>
+    <t>He thong chua co Trip nao</t>
+  </si>
+  <si>
+    <t>UC34 - Quan ly Account</t>
+  </si>
+  <si>
+    <t>TC_FR96_POS</t>
+  </si>
+  <si>
+    <t>[Positive] Quan ly Account (FR96)</t>
+  </si>
+  <si>
+    <t>[Positive] Quan ly Account</t>
+  </si>
+  <si>
+    <t>Administrator co permission.</t>
+  </si>
+  <si>
+    <t>1.Mo danh sach Account 2.View/Search</t>
+  </si>
+  <si>
+    <t>Account data</t>
+  </si>
+  <si>
+    <t>He thong hien thi va tim kiem Account trong pham vi.</t>
+  </si>
+  <si>
+    <t>TC_FR96_LOCK</t>
+  </si>
+  <si>
+    <t>[Positive] Lock Account va ghi AuditLog (FR104)</t>
+  </si>
+  <si>
+    <t>[Positive] Lock Account va ghi AuditLog</t>
+  </si>
+  <si>
+    <t>Admin co permission; Account ACTIVE.</t>
+  </si>
+  <si>
+    <t>1.Lock Account 2.Kiem tra</t>
+  </si>
+  <si>
+    <t>Account ACTIVE</t>
+  </si>
+  <si>
+    <t>Account bi lock/disable theo thao tac; AuditLog ghi nhan.</t>
+  </si>
+  <si>
+    <t>High (NFR06)</t>
+  </si>
+  <si>
+    <t>TC_FR96_UNLOCK</t>
+  </si>
+  <si>
+    <t>[Positive] Unlock Account va ghi AuditLog (FR104)</t>
+  </si>
+  <si>
+    <t>[Positive] Unlock Account va ghi AuditLog</t>
+  </si>
+  <si>
+    <t>Account dang bi lock.</t>
+  </si>
+  <si>
+    <t>1.Unlock Account 2.Kiem tra</t>
+  </si>
+  <si>
+    <t>Account locked</t>
+  </si>
+  <si>
+    <t>Account duoc mo khoa; AuditLog ghi nhan.</t>
+  </si>
+  <si>
+    <t>TC_FR96_DISABLE</t>
+  </si>
+  <si>
+    <t>[Positive] Disable Account va ghi AuditLog (FR104)</t>
+  </si>
+  <si>
+    <t>[Positive] Disable Account va ghi AuditLog</t>
+  </si>
+  <si>
+    <t>Account ACTIVE.</t>
+  </si>
+  <si>
+    <t>1.Disable Account</t>
+  </si>
+  <si>
+    <t>Account chuyen trang thai vo hieu; AuditLog ghi nhan.</t>
+  </si>
+  <si>
+    <t>TC_FR96_ENABLE</t>
+  </si>
+  <si>
+    <t>[Positive] Enable Account va ghi AuditLog (FR104)</t>
+  </si>
+  <si>
+    <t>[Positive] Enable Account va ghi AuditLog</t>
+  </si>
+  <si>
+    <t>Account disabled.</t>
+  </si>
+  <si>
+    <t>1.Enable Account</t>
+  </si>
+  <si>
+    <t>Account duoc enable; AuditLog ghi nhan.</t>
+  </si>
+  <si>
+    <t>TC_FR98_ASSIGN</t>
+  </si>
+  <si>
+    <t>[Positive] Gán Role cho Account (FR98,105)</t>
+  </si>
+  <si>
+    <t>[Positive] Gán Role cho Account</t>
+  </si>
+  <si>
+    <t>Admin co permission; Role ton tai.</t>
+  </si>
+  <si>
+    <t>1.Chon Account 2.Gan Role 3.Luu</t>
+  </si>
+  <si>
+    <t>Role hop le</t>
+  </si>
+  <si>
+    <t>Role duoc gan; thao tac nhay cam duoc AuditLog.</t>
+  </si>
+  <si>
+    <t>TC_FR96_DENY</t>
+  </si>
+  <si>
+    <t>[Negative] Khong cho user khong co quyen quan ly Account (FR96,100)</t>
+  </si>
+  <si>
+    <t>[Negative] Khong cho user khong co quyen quan ly Account</t>
+  </si>
+  <si>
+    <t>User khong co permission admin.</t>
+  </si>
+  <si>
+    <t>1.Gui request quan ly Account</t>
+  </si>
+  <si>
+    <t>He thong reject/403.</t>
+  </si>
+  <si>
+    <t>TC_FR104_AUDIT</t>
+  </si>
+  <si>
+    <t>[Positive] Ghi AuditLog cho thao tac Account nhay cam (FR104,105)</t>
+  </si>
+  <si>
+    <t>[Positive] Ghi AuditLog cho thao tac Account nhay cam</t>
+  </si>
+  <si>
+    <t>Admin thuc hien lock/unlock/disable/enable/assign role.</t>
+  </si>
+  <si>
+    <t>1.Thuc hien thao tac 2.Mo AuditLog</t>
+  </si>
+  <si>
+    <t>Action nhay cam</t>
+  </si>
+  <si>
+    <t>AuditLog luu actor, action, target, timestamp, details.</t>
+  </si>
+  <si>
+    <t>High (NFR06) (BRULE25)</t>
+  </si>
+  <si>
+    <t>UC35 - Quan ly Role</t>
+  </si>
+  <si>
+    <t>TC_FR96_ROLE_CREATE</t>
+  </si>
+  <si>
+    <t>[Positive] Tao Role (FR96)</t>
+  </si>
+  <si>
+    <t>[Positive] Tao Role</t>
+  </si>
+  <si>
+    <t>Admin co permission.</t>
+  </si>
+  <si>
+    <t>1.Nhap Role 2.Luu</t>
+  </si>
+  <si>
+    <t>Role moi hop le</t>
+  </si>
+  <si>
+    <t>Role duoc CREATE.</t>
+  </si>
+  <si>
+    <t>TC_FR96_ROLE_READ</t>
+  </si>
+  <si>
+    <t>[Positive] Xem Role (FR96)</t>
+  </si>
+  <si>
+    <t>[Positive] Xem Role</t>
+  </si>
+  <si>
+    <t>1.Mo danh sach Role</t>
+  </si>
+  <si>
+    <t>Role data</t>
+  </si>
+  <si>
+    <t>Role duoc hien thi.</t>
+  </si>
+  <si>
+    <t>TC_FR96_ROLE_UPDATE</t>
+  </si>
+  <si>
+    <t>[Positive] Cap nhat Role (FR96)</t>
+  </si>
+  <si>
+    <t>[Positive] Cap nhat Role</t>
+  </si>
+  <si>
+    <t>Role ton tai; admin co permission.</t>
+  </si>
+  <si>
+    <t>1.Sua Role 2.Luu</t>
+  </si>
+  <si>
+    <t>Role data moi</t>
+  </si>
+  <si>
+    <t>Role duoc UPDATE.</t>
+  </si>
+  <si>
+    <t>TC_FR96_ROLE_ASSIGN</t>
+  </si>
+  <si>
+    <t>[Positive] Gan Role theo chuc nang Role (FR98)</t>
+  </si>
+  <si>
+    <t>[Positive] Gan Role theo chuc nang Role</t>
+  </si>
+  <si>
+    <t>1.Chon user 2.Gan Role</t>
+  </si>
+  <si>
+    <t>Role duoc gan cho user.</t>
+  </si>
+  <si>
+    <t>TC_FR96_ROLE_PROTECT</t>
+  </si>
+  <si>
+    <t>[Negative] Khong xoa Role he thong neu gay mat toan ven quyen (FR96)</t>
+  </si>
+  <si>
+    <t>[Negative] Khong xoa Role he thong neu gay mat toan ven quyen</t>
+  </si>
+  <si>
+    <t>Role he thong dang duoc su dung.</t>
+  </si>
+  <si>
+    <t>1.Yeu cau xoa Role</t>
+  </si>
+  <si>
+    <t>System Role dang duoc su dung</t>
+  </si>
+  <si>
+    <t>He thong khong cho phep xoa neu gay mat tinh toan ven quyen.</t>
+  </si>
+  <si>
+    <t>UC36 - Quan ly Permission</t>
+  </si>
+  <si>
+    <t>TC_FR97_POS</t>
+  </si>
+  <si>
+    <t>[Positive] Quan ly Permission (FR97)</t>
+  </si>
+  <si>
+    <t>[Positive] Quan ly Permission</t>
+  </si>
+  <si>
+    <t>1.View Permission</t>
+  </si>
+  <si>
+    <t>Permission data</t>
+  </si>
+  <si>
+    <t>He thong hien thi Permission.</t>
+  </si>
+  <si>
+    <t>TC_FR97_CREATE</t>
+  </si>
+  <si>
+    <t>[Positive] Tao Permission (FR97)</t>
+  </si>
+  <si>
+    <t>[Positive] Tao Permission</t>
+  </si>
+  <si>
+    <t>1.Tao Permission 2.Luu</t>
+  </si>
+  <si>
+    <t>Permission duoc CREATE.</t>
+  </si>
+  <si>
+    <t>TC_FR97_UPDATE</t>
+  </si>
+  <si>
+    <t>[Positive] Cap nhat Permission (FR97)</t>
+  </si>
+  <si>
+    <t>[Positive] Cap nhat Permission</t>
+  </si>
+  <si>
+    <t>Permission ton tai.</t>
+  </si>
+  <si>
+    <t>1.Sua Permission 2.Luu</t>
+  </si>
+  <si>
+    <t>Du lieu moi</t>
+  </si>
+  <si>
+    <t>Permission duoc UPDATE.</t>
+  </si>
+  <si>
+    <t>TC_FR97_ASSIGN</t>
+  </si>
+  <si>
+    <t>[Positive] Gan Permission cho Role (FR97)</t>
+  </si>
+  <si>
+    <t>[Positive] Gan Permission cho Role</t>
+  </si>
+  <si>
+    <t>Role va Permission ton tai.</t>
+  </si>
+  <si>
+    <t>1.Chon Role 2.Assign Permission</t>
+  </si>
+  <si>
+    <t>Role + Permission</t>
+  </si>
+  <si>
+    <t>Permission duoc gan cho Role.</t>
+  </si>
+  <si>
+    <t>TC_FR99_CHECK</t>
+  </si>
+  <si>
+    <t>[Positive] Backend kiem tra Permission (FR99)</t>
+  </si>
+  <si>
+    <t>[Positive] Backend kiem tra Permission</t>
+  </si>
+  <si>
+    <t>User co permission hop le.</t>
+  </si>
+  <si>
+    <t>1.Gui request can permission</t>
+  </si>
+  <si>
+    <t>Backend cho phep request.</t>
+  </si>
+  <si>
+    <t>High (NFR02) (BRULE23, BRULE24)</t>
+  </si>
+  <si>
+    <t>TC_FR100_DENY</t>
+  </si>
+  <si>
+    <t>[Negative] Chan truy cap trai quyen (FR100)</t>
+  </si>
+  <si>
+    <t>[Negative] Chan truy cap trai quyen</t>
+  </si>
+  <si>
+    <t>1.Gui request admin</t>
+  </si>
+  <si>
+    <t>Permission thieu</t>
+  </si>
+  <si>
+    <t>Backend reject/403, khong tin permission tu frontend.</t>
+  </si>
+  <si>
+    <t>TC_LOG_AUTHZ_FAIL</t>
+  </si>
+  <si>
+    <t>[Negative] Ghi log authorization failure khi bi tu choi (FR100)</t>
+  </si>
+  <si>
+    <t>[Negative] Ghi log authorization failure khi bi tu choi</t>
+  </si>
+  <si>
+    <t>User thieu permission.</t>
+  </si>
+  <si>
+    <t>1.Gui request trai quyen 2.Kiem tra log</t>
+  </si>
+  <si>
+    <t>He thong reject/403 va ghi log authorization failure.</t>
+  </si>
+  <si>
+    <t>UC37 - Xem AuditLog</t>
+  </si>
+  <si>
+    <t>TC_FR101_POS</t>
+  </si>
+  <si>
+    <t>[Positive] Ghi AuditLog khi Login theo chinh sach (FR101)</t>
+  </si>
+  <si>
+    <t>[Positive] Ghi AuditLog khi Login theo chinh sach</t>
+  </si>
+  <si>
+    <t>User login; chinh sach AuditLog ap dung.</t>
+  </si>
+  <si>
+    <t>1.Login 2.Kiem tra AuditLog</t>
+  </si>
+  <si>
+    <t>Login event</t>
+  </si>
+  <si>
+    <t>AuditLog ghi actor/action/target/timestamp/details phu hop.</t>
+  </si>
+  <si>
+    <t>TC_FR102_POS</t>
+  </si>
+  <si>
+    <t>[Positive] Ghi AuditLog khi thay doi Role (FR102)</t>
+  </si>
+  <si>
+    <t>[Positive] Ghi AuditLog khi thay doi Role</t>
+  </si>
+  <si>
+    <t>Admin thay doi Role.</t>
+  </si>
+  <si>
+    <t>1.Update/assign Role 2.Kiem tra log</t>
+  </si>
+  <si>
+    <t>Role change</t>
+  </si>
+  <si>
+    <t>AuditLog duoc ghi.</t>
+  </si>
+  <si>
+    <t>TC_FR103_POS</t>
+  </si>
+  <si>
+    <t>[Positive] Ghi AuditLog khi thay doi Permission (FR103)</t>
+  </si>
+  <si>
+    <t>[Positive] Ghi AuditLog khi thay doi Permission</t>
+  </si>
+  <si>
+    <t>Admin thay doi Permission.</t>
+  </si>
+  <si>
+    <t>1.Update/assign Permission 2.Kiem tra log</t>
+  </si>
+  <si>
+    <t>Permission change</t>
+  </si>
+  <si>
+    <t>TC_FR104_POS</t>
+  </si>
+  <si>
+    <t>[Positive] Ghi AuditLog khi lock/unlock Account (FR104)</t>
+  </si>
+  <si>
+    <t>[Positive] Ghi AuditLog khi lock/unlock Account</t>
+  </si>
+  <si>
+    <t>Admin co quyen.</t>
+  </si>
+  <si>
+    <t>1.Lock/Unlock 2.Kiem tra log</t>
+  </si>
+  <si>
+    <t>Account status change</t>
+  </si>
+  <si>
+    <t>TC_FR105_POS</t>
+  </si>
+  <si>
+    <t>[Positive] Ghi AuditLog thao tac quan tri quan trong (FR105)</t>
+  </si>
+  <si>
+    <t>[Positive] Ghi AuditLog thao tac quan tri quan trong</t>
+  </si>
+  <si>
+    <t>Admin thuc hien thao tac nhay cam.</t>
+  </si>
+  <si>
+    <t>1.Thuc hien action 2.Kiem tra log</t>
+  </si>
+  <si>
+    <t>Admin action</t>
+  </si>
+  <si>
+    <t>TC_FR105_NOEDIT</t>
+  </si>
+  <si>
+    <t>[Negative] Khong cho sua AuditLog qua UI thong thuong (FR105)</t>
+  </si>
+  <si>
+    <t>[Negative] Khong cho sua AuditLog qua UI thong thuong</t>
+  </si>
+  <si>
+    <t>AuditLog ton tai.</t>
+  </si>
+  <si>
+    <t>1.Mo AuditLog 2.Tim thao tac Edit</t>
+  </si>
+  <si>
+    <t>AuditLog record</t>
+  </si>
+  <si>
+    <t>UI khong cung cap thao tac sua AuditLog.</t>
+  </si>
+  <si>
+    <t>TC_AUDIT_EMPTY</t>
+  </si>
+  <si>
+    <t>[Exception] Xem AuditLog khi chua co ban ghi nao (UC37)</t>
+  </si>
+  <si>
+    <t>[Exception] Xem AuditLog khi chua co ban ghi nao</t>
+  </si>
+  <si>
+    <t>Admin dang nhap; he thong chua ghi AuditLog nao.</t>
+  </si>
+  <si>
+    <t>1.Goi API xem danh sach AuditLog</t>
+  </si>
+  <si>
+    <t>Chua co AuditLog nao</t>
   </si>
   <si>
     <t>Low</t>
   </si>
   <si>
-    <t>UC30 - Quan ly Customer</t>
-  </si>
-  <si>
-    <t>TC_FR88_POS</t>
-  </si>
-  <si>
-    <t>[Positive] Operations xem Customer (FR88)</t>
-  </si>
-  <si>
-    <t>[Positive] Operations xem Customer</t>
-  </si>
-  <si>
-    <t>1.Mo Customers</t>
-  </si>
-  <si>
-    <t>Customer data</t>
-  </si>
-  <si>
-    <t>He thong hien thi Customer trong pham vi quyen.</t>
-  </si>
-  <si>
-    <t>TC_FR88_SEARCH</t>
-  </si>
-  <si>
-    <t>[Positive] Tim kiem Customer (FR88)</t>
-  </si>
-  <si>
-    <t>[Positive] Tim kiem Customer</t>
-  </si>
-  <si>
-    <t>Co nhieu Customer.</t>
-  </si>
-  <si>
-    <t>1.Nhap dieu kien tim kiem</t>
-  </si>
-  <si>
-    <t>Tu khoa hop le</t>
-  </si>
-  <si>
-    <t>He thong tra dung Customer phu hop.</t>
-  </si>
-  <si>
-    <t>TC_FR88_FILTER</t>
-  </si>
-  <si>
-    <t>[Positive] Loc Customer (FR88)</t>
-  </si>
-  <si>
-    <t>[Positive] Loc Customer</t>
-  </si>
-  <si>
-    <t>Co du lieu Customer.</t>
-  </si>
-  <si>
-    <t>1.Chon bo loc</t>
-  </si>
-  <si>
-    <t>Bo loc hop le</t>
-  </si>
-  <si>
-    <t>He thong tra dung tap Customer phu hop.</t>
-  </si>
-  <si>
-    <t>TC_FR88_DETAIL</t>
-  </si>
-  <si>
-    <t>[Positive] Xem chi tiet Customer (FR88)</t>
-  </si>
-  <si>
-    <t>[Positive] Xem chi tiet Customer</t>
-  </si>
-  <si>
-    <t>1.Chon Customer</t>
-  </si>
-  <si>
-    <t>customerId hop le</t>
-  </si>
-  <si>
-    <t>He thong hien thi chi tiet Customer.</t>
-  </si>
-  <si>
-    <t>TC_FR88_DENY</t>
-  </si>
-  <si>
-    <t>[Negative] Khong truy cap Customer khi thieu permission (FR88)</t>
-  </si>
-  <si>
-    <t>[Negative] Khong truy cap Customer khi thieu permission</t>
-  </si>
-  <si>
-    <t>TC_FR88_NORESULT</t>
-  </si>
-  <si>
-    <t>[Exception] Tim kiem/loc Customer khong khop ket qua nao (FR88)</t>
-  </si>
-  <si>
-    <t>[Exception] Tim kiem/loc Customer khong khop ket qua nao</t>
-  </si>
-  <si>
-    <t>Operations Staff co permission xem Customer.</t>
-  </si>
-  <si>
-    <t>1.Nhap tu khoa tim kiem/dieu kien loc khong khop Customer nao 2.Xem ket qua</t>
-  </si>
-  <si>
-    <t>Tu khoa/dieu kien khong khop du lieu nao</t>
-  </si>
-  <si>
-    <t>He thong tra ve danh sach rong; khong loi; khong tra nham du lieu khac.</t>
-  </si>
-  <si>
-    <t>UC31 - Quan ly Driver</t>
-  </si>
-  <si>
-    <t>TC_FR89_POS</t>
-  </si>
-  <si>
-    <t>[Positive] Operations xem Driver va trang thai (FR89,93)</t>
-  </si>
-  <si>
-    <t>[Positive] Operations xem Driver va trang thai</t>
-  </si>
-  <si>
-    <t>1.Mo Drivers 2.Xem status</t>
-  </si>
-  <si>
-    <t>Driver data</t>
-  </si>
-  <si>
-    <t>He thong hien thi Driver va status dung.</t>
-  </si>
-  <si>
-    <t>TC_FR89_SEARCH</t>
-  </si>
-  <si>
-    <t>[Positive] Tim kiem Driver (FR89)</t>
-  </si>
-  <si>
-    <t>[Positive] Tim kiem Driver</t>
-  </si>
-  <si>
-    <t>Co nhieu Driver.</t>
-  </si>
-  <si>
-    <t>1.Nhap tu khoa</t>
-  </si>
-  <si>
-    <t>He thong tra dung Driver.</t>
-  </si>
-  <si>
-    <t>TC_FR89_FILTER</t>
-  </si>
-  <si>
-    <t>[Positive] Loc Driver (FR89)</t>
-  </si>
-  <si>
-    <t>[Positive] Loc Driver</t>
-  </si>
-  <si>
-    <t>Co du lieu Driver.</t>
-  </si>
-  <si>
-    <t>TC_FR89_DETAIL</t>
-  </si>
-  <si>
-    <t>[Positive] Xem chi tiet Driver (FR89)</t>
-  </si>
-  <si>
-    <t>[Positive] Xem chi tiet Driver</t>
-  </si>
-  <si>
-    <t>1.Chon Driver</t>
-  </si>
-  <si>
-    <t>driverId</t>
-  </si>
-  <si>
-    <t>He thong hien thi chi tiet Driver.</t>
-  </si>
-  <si>
-    <t>TC_FR89_DENY</t>
-  </si>
-  <si>
-    <t>[Negative] Thieu permission khi xem Driver (FR89)</t>
-  </si>
-  <si>
-    <t>[Negative] Thieu permission khi xem Driver</t>
-  </si>
-  <si>
-    <t>1.Mo Drivers</t>
-  </si>
-  <si>
-    <t>Khong permission</t>
-  </si>
-  <si>
-    <t>TC_FR89_NORESULT</t>
-  </si>
-  <si>
-    <t>[Exception] Tim kiem/loc Driver khong khop ket qua nao (FR89)</t>
-  </si>
-  <si>
-    <t>[Exception] Tim kiem/loc Driver khong khop ket qua nao</t>
-  </si>
-  <si>
-    <t>Operations Staff co permission xem Driver.</t>
-  </si>
-  <si>
-    <t>1.Nhap tu khoa tim kiem/dieu kien loc khong khop Driver nao 2.Xem ket qua</t>
-  </si>
-  <si>
-    <t>UC32 - Quan ly Vehicle</t>
-  </si>
-  <si>
-    <t>TC_FR90_POS</t>
-  </si>
-  <si>
-    <t>[Positive] Operations xem va quan ly Vehicle (FR90)</t>
-  </si>
-  <si>
-    <t>[Positive] Operations xem va quan ly Vehicle</t>
-  </si>
-  <si>
-    <t>1.Mo Vehicles 2.Xem detail</t>
-  </si>
-  <si>
-    <t>Vehicle data</t>
-  </si>
-  <si>
-    <t>He thong cho xem Vehicle trong pham vi.</t>
-  </si>
-  <si>
-    <t>TC_FR90_SEARCH</t>
-  </si>
-  <si>
-    <t>[Positive] Tim kiem Vehicle (FR90)</t>
-  </si>
-  <si>
-    <t>[Positive] Tim kiem Vehicle</t>
-  </si>
-  <si>
-    <t>Co nhieu Vehicle.</t>
-  </si>
-  <si>
-    <t>Tu khoa</t>
-  </si>
-  <si>
-    <t>He thong tra dung Vehicle.</t>
-  </si>
-  <si>
-    <t>TC_FR90_FILTER</t>
-  </si>
-  <si>
-    <t>[Positive] Loc Vehicle (FR90)</t>
-  </si>
-  <si>
-    <t>[Positive] Loc Vehicle</t>
-  </si>
-  <si>
-    <t>Co Vehicle.</t>
-  </si>
-  <si>
-    <t>1.Chon filter</t>
-  </si>
-  <si>
-    <t>Filter hop le</t>
-  </si>
-  <si>
-    <t>TC_FR90_STATUS</t>
-  </si>
-  <si>
-    <t>[Positive] Cap nhat trang thai Vehicle (FR90)</t>
-  </si>
-  <si>
-    <t>[Positive] Cap nhat trang thai Vehicle</t>
-  </si>
-  <si>
-    <t>Staff co permission; Vehicle ton tai.</t>
-  </si>
-  <si>
-    <t>1.Chon Vehicle 2.Update status</t>
-  </si>
-  <si>
-    <t>ACTIVE/INACTIVE</t>
-  </si>
-  <si>
-    <t>Trang thai Vehicle duoc UPDATE theo quyen.</t>
-  </si>
-  <si>
-    <t>TC_FR90_DENY</t>
-  </si>
-  <si>
-    <t>[Negative] Thieu permission khi quan ly Vehicle (FR90)</t>
-  </si>
-  <si>
-    <t>[Negative] Thieu permission khi quan ly Vehicle</t>
-  </si>
-  <si>
-    <t>1.Update Vehicle</t>
-  </si>
-  <si>
-    <t>TC_FR90_NORESULT</t>
-  </si>
-  <si>
-    <t>[Exception] Tim kiem/loc Vehicle khong khop ket qua nao (FR90)</t>
-  </si>
-  <si>
-    <t>[Exception] Tim kiem/loc Vehicle khong khop ket qua nao</t>
-  </si>
-  <si>
-    <t>Operations Staff co permission xem Vehicle.</t>
-  </si>
-  <si>
-    <t>1.Nhap tu khoa tim kiem/dieu kien loc khong khop Vehicle nao 2.Xem ket qua</t>
-  </si>
-  <si>
-    <t>UC33 - Theo doi Trip</t>
-  </si>
-  <si>
-    <t>TC_FR91_POS</t>
-  </si>
-  <si>
-    <t>[Positive] Xem danh sach Trip (FR91)</t>
-  </si>
-  <si>
-    <t>[Positive] Xem danh sach Trip</t>
-  </si>
-  <si>
-    <t>1.Mo Trips</t>
-  </si>
-  <si>
-    <t>Trip data</t>
-  </si>
-  <si>
-    <t>He thong hien thi danh sach Trip trong pham vi.</t>
-  </si>
-  <si>
-    <t>TC_FR92_POS</t>
-  </si>
-  <si>
-    <t>[Positive] Xem chi tiet Trip (FR92)</t>
-  </si>
-  <si>
-    <t>[Positive] Xem chi tiet Trip</t>
-  </si>
-  <si>
-    <t>1.Chon Trip</t>
-  </si>
-  <si>
-    <t>tripId</t>
-  </si>
-  <si>
-    <t>He thong hien thi Trip ID, Customer, Driver, Vehicle, pickup, destination, status, fare, createdAt.</t>
-  </si>
-  <si>
-    <t>TC_FR93_POS</t>
-  </si>
-  <si>
-    <t>[Positive] Theo doi Driver (FR93)</t>
-  </si>
-  <si>
-    <t>[Positive] Theo doi Driver</t>
-  </si>
-  <si>
-    <t>1.Mo theo doi Driver</t>
-  </si>
-  <si>
-    <t>Driver current status/location</t>
-  </si>
-  <si>
-    <t>He thong hien thi thong tin theo doi Driver trong pham vi.</t>
-  </si>
-  <si>
-    <t>TC_FR91_PAG</t>
-  </si>
-  <si>
-    <t>[Positive] Danh sach lon co pagination (FR91)</t>
-  </si>
-  <si>
-    <t>[Positive] Danh sach lon co pagination</t>
-  </si>
-  <si>
-    <t>Danh sach Trip lon.</t>
-  </si>
-  <si>
-    <t>1.Mo danh sach 2.Chuyen trang</t>
-  </si>
-  <si>
-    <t>Nhieu ban ghi</t>
-  </si>
-  <si>
-    <t>He thong phan trang va khong can load tat ca record vao mot trang (NFR10).</t>
-  </si>
-  <si>
-    <t>TC_FR91_DENY</t>
-  </si>
-  <si>
-    <t>[Negative] Thieu permission khi theo doi Trip (FR91,92,93)</t>
-  </si>
-  <si>
-    <t>[Negative] Thieu permission khi theo doi Trip</t>
-  </si>
-  <si>
-    <t>TC_FR55_POS</t>
-  </si>
-  <si>
-    <t>[Positive] Customer xem vi tri Driver (FR55)</t>
-  </si>
-  <si>
-    <t>[Positive] Customer xem vi tri Driver</t>
-  </si>
-  <si>
-    <t>Customer dang co Trip va Driver co current location.</t>
-  </si>
-  <si>
-    <t>1.Mo tracking Trip</t>
-  </si>
-  <si>
-    <t>Driver.currentLatitude/currentLongitude</t>
-  </si>
-  <si>
-    <t>He thong hien thi vi tri hien tai cua Driver cho Customer theo quyen.</t>
-  </si>
-  <si>
-    <t>TC_FR56_POS</t>
-  </si>
-  <si>
-    <t>[Positive] Operations Staff xem vi tri Driver (FR56)</t>
-  </si>
-  <si>
-    <t>[Positive] Operations Staff xem vi tri Driver</t>
-  </si>
-  <si>
-    <t>Staff co permission; Driver co current location.</t>
-  </si>
-  <si>
-    <t>1.Mo tracking Driver</t>
-  </si>
-  <si>
-    <t>Driver location</t>
-  </si>
-  <si>
-    <t>He thong hien thi vi tri hien tai cua Driver cho Staff.</t>
-  </si>
-  <si>
-    <t>TC_NFR08_RESPONSE</t>
-  </si>
-  <si>
-    <t>[Positive] Chuc nang thong thuong phan hoi phu hop moi truong MVP (FR91,92,93)</t>
-  </si>
-  <si>
-    <t>[Positive] Chuc nang thong thuong phan hoi phu hop moi truong MVP</t>
-  </si>
-  <si>
-    <t>He thong o moi truong MVP.</t>
-  </si>
-  <si>
-    <t>1.Thuc hien thao tac thong thuong 2.Do thoi gian phan hoi</t>
-  </si>
-  <si>
-    <t>Request thong thuong</t>
-  </si>
-  <si>
-    <t>Thoi gian phan hoi dap ung benchmark phu hop moi truong MVP; khong co timeout bat thuong (NFR08).</t>
-  </si>
-  <si>
-    <t>TC_FR91_EMPTY</t>
-  </si>
-  <si>
-    <t>[Exception] Operations xem danh sach Trip khi he thong chua co Trip nao (FR91)</t>
-  </si>
-  <si>
-    <t>[Exception] Operations xem danh sach Trip khi he thong chua co Trip nao</t>
-  </si>
-  <si>
-    <t>Operations Staff co permission; he thong chua co Trip nao.</t>
-  </si>
-  <si>
-    <t>1.Goi API xem danh sach Trip</t>
-  </si>
-  <si>
-    <t>He thong chua co Trip nao</t>
-  </si>
-  <si>
-    <t>UC34 - Quan ly Account</t>
-  </si>
-  <si>
-    <t>TC_FR96_POS</t>
-  </si>
-  <si>
-    <t>[Positive] Quan ly Account (FR96)</t>
-  </si>
-  <si>
-    <t>[Positive] Quan ly Account</t>
-  </si>
-  <si>
-    <t>Administrator co permission.</t>
-  </si>
-  <si>
-    <t>1.Mo danh sach Account 2.View/Search</t>
-  </si>
-  <si>
-    <t>Account data</t>
-  </si>
-  <si>
-    <t>He thong hien thi va tim kiem Account trong pham vi.</t>
-  </si>
-  <si>
-    <t>TC_FR96_LOCK</t>
-  </si>
-  <si>
-    <t>[Positive] Lock Account va ghi AuditLog (FR104)</t>
-  </si>
-  <si>
-    <t>[Positive] Lock Account va ghi AuditLog</t>
-  </si>
-  <si>
-    <t>Admin co permission; Account ACTIVE.</t>
-  </si>
-  <si>
-    <t>1.Lock Account 2.Kiem tra</t>
-  </si>
-  <si>
-    <t>Account ACTIVE</t>
-  </si>
-  <si>
-    <t>Account bi lock/disable theo thao tac; AuditLog ghi nhan.</t>
-  </si>
-  <si>
-    <t>High (NFR06)</t>
-  </si>
-  <si>
-    <t>TC_FR96_UNLOCK</t>
-  </si>
-  <si>
-    <t>[Positive] Unlock Account va ghi AuditLog (FR104)</t>
-  </si>
-  <si>
-    <t>[Positive] Unlock Account va ghi AuditLog</t>
-  </si>
-  <si>
-    <t>Account dang bi lock.</t>
-  </si>
-  <si>
-    <t>1.Unlock Account 2.Kiem tra</t>
-  </si>
-  <si>
-    <t>Account locked</t>
-  </si>
-  <si>
-    <t>Account duoc mo khoa; AuditLog ghi nhan.</t>
-  </si>
-  <si>
-    <t>TC_FR96_DISABLE</t>
-  </si>
-  <si>
-    <t>[Positive] Disable Account va ghi AuditLog (FR104)</t>
-  </si>
-  <si>
-    <t>[Positive] Disable Account va ghi AuditLog</t>
-  </si>
-  <si>
-    <t>Account ACTIVE.</t>
-  </si>
-  <si>
-    <t>1.Disable Account</t>
-  </si>
-  <si>
-    <t>Account chuyen trang thai vo hieu; AuditLog ghi nhan.</t>
-  </si>
-  <si>
-    <t>TC_FR96_ENABLE</t>
-  </si>
-  <si>
-    <t>[Positive] Enable Account va ghi AuditLog (FR104)</t>
-  </si>
-  <si>
-    <t>[Positive] Enable Account va ghi AuditLog</t>
-  </si>
-  <si>
-    <t>Account disabled.</t>
-  </si>
-  <si>
-    <t>1.Enable Account</t>
-  </si>
-  <si>
-    <t>Account duoc enable; AuditLog ghi nhan.</t>
-  </si>
-  <si>
-    <t>TC_FR98_ASSIGN</t>
-  </si>
-  <si>
-    <t>[Positive] Gán Role cho Account (FR98,105)</t>
-  </si>
-  <si>
-    <t>[Positive] Gán Role cho Account</t>
-  </si>
-  <si>
-    <t>Admin co permission; Role ton tai.</t>
-  </si>
-  <si>
-    <t>1.Chon Account 2.Gan Role 3.Luu</t>
-  </si>
-  <si>
-    <t>Role hop le</t>
-  </si>
-  <si>
-    <t>Role duoc gan; thao tac nhay cam duoc AuditLog.</t>
-  </si>
-  <si>
-    <t>TC_FR96_DENY</t>
-  </si>
-  <si>
-    <t>[Negative] Khong cho user khong co quyen quan ly Account (FR96,100)</t>
-  </si>
-  <si>
-    <t>[Negative] Khong cho user khong co quyen quan ly Account</t>
-  </si>
-  <si>
-    <t>User khong co permission admin.</t>
-  </si>
-  <si>
-    <t>1.Gui request quan ly Account</t>
-  </si>
-  <si>
-    <t>He thong reject/403.</t>
-  </si>
-  <si>
-    <t>TC_FR104_AUDIT</t>
-  </si>
-  <si>
-    <t>[Positive] Ghi AuditLog cho thao tac Account nhay cam (FR104,105)</t>
-  </si>
-  <si>
-    <t>[Positive] Ghi AuditLog cho thao tac Account nhay cam</t>
-  </si>
-  <si>
-    <t>Admin thuc hien lock/unlock/disable/enable/assign role.</t>
-  </si>
-  <si>
-    <t>1.Thuc hien thao tac 2.Mo AuditLog</t>
-  </si>
-  <si>
-    <t>Action nhay cam</t>
-  </si>
-  <si>
-    <t>AuditLog luu actor, action, target, timestamp, details.</t>
-  </si>
-  <si>
-    <t>High (NFR06) (BRULE25)</t>
-  </si>
-  <si>
-    <t>UC35 - Quan ly Role</t>
-  </si>
-  <si>
-    <t>TC_FR96_ROLE_CREATE</t>
-  </si>
-  <si>
-    <t>[Positive] Tao Role (FR96)</t>
-  </si>
-  <si>
-    <t>[Positive] Tao Role</t>
-  </si>
-  <si>
-    <t>Admin co permission.</t>
-  </si>
-  <si>
-    <t>1.Nhap Role 2.Luu</t>
-  </si>
-  <si>
-    <t>Role moi hop le</t>
-  </si>
-  <si>
-    <t>Role duoc CREATE.</t>
-  </si>
-  <si>
-    <t>TC_FR96_ROLE_READ</t>
-  </si>
-  <si>
-    <t>[Positive] Xem Role (FR96)</t>
-  </si>
-  <si>
-    <t>[Positive] Xem Role</t>
-  </si>
-  <si>
-    <t>1.Mo danh sach Role</t>
-  </si>
-  <si>
-    <t>Role data</t>
-  </si>
-  <si>
-    <t>Role duoc hien thi.</t>
-  </si>
-  <si>
-    <t>TC_FR96_ROLE_UPDATE</t>
-  </si>
-  <si>
-    <t>[Positive] Cap nhat Role (FR96)</t>
-  </si>
-  <si>
-    <t>[Positive] Cap nhat Role</t>
-  </si>
-  <si>
-    <t>Role ton tai; admin co permission.</t>
-  </si>
-  <si>
-    <t>1.Sua Role 2.Luu</t>
-  </si>
-  <si>
-    <t>Role data moi</t>
-  </si>
-  <si>
-    <t>Role duoc UPDATE.</t>
-  </si>
-  <si>
-    <t>TC_FR96_ROLE_ASSIGN</t>
-  </si>
-  <si>
-    <t>[Positive] Gan Role theo chuc nang Role (FR98)</t>
-  </si>
-  <si>
-    <t>[Positive] Gan Role theo chuc nang Role</t>
-  </si>
-  <si>
-    <t>1.Chon user 2.Gan Role</t>
-  </si>
-  <si>
-    <t>Role duoc gan cho user.</t>
-  </si>
-  <si>
-    <t>TC_FR96_ROLE_PROTECT</t>
-  </si>
-  <si>
-    <t>[Negative] Khong xoa Role he thong neu gay mat toan ven quyen (FR96)</t>
-  </si>
-  <si>
-    <t>[Negative] Khong xoa Role he thong neu gay mat toan ven quyen</t>
-  </si>
-  <si>
-    <t>Role he thong dang duoc su dung.</t>
-  </si>
-  <si>
-    <t>1.Yeu cau xoa Role</t>
-  </si>
-  <si>
-    <t>System Role dang duoc su dung</t>
-  </si>
-  <si>
-    <t>He thong khong cho phep xoa neu gay mat tinh toan ven quyen.</t>
-  </si>
-  <si>
-    <t>UC36 - Quan ly Permission</t>
-  </si>
-  <si>
-    <t>TC_FR97_POS</t>
-  </si>
-  <si>
-    <t>[Positive] Quan ly Permission (FR97)</t>
-  </si>
-  <si>
-    <t>[Positive] Quan ly Permission</t>
-  </si>
-  <si>
-    <t>1.View Permission</t>
-  </si>
-  <si>
-    <t>Permission data</t>
-  </si>
-  <si>
-    <t>He thong hien thi Permission.</t>
-  </si>
-  <si>
-    <t>TC_FR97_CREATE</t>
-  </si>
-  <si>
-    <t>[Positive] Tao Permission (FR97)</t>
-  </si>
-  <si>
-    <t>[Positive] Tao Permission</t>
-  </si>
-  <si>
-    <t>1.Tao Permission 2.Luu</t>
-  </si>
-  <si>
-    <t>Permission duoc CREATE.</t>
-  </si>
-  <si>
-    <t>TC_FR97_UPDATE</t>
-  </si>
-  <si>
-    <t>[Positive] Cap nhat Permission (FR97)</t>
-  </si>
-  <si>
-    <t>[Positive] Cap nhat Permission</t>
-  </si>
-  <si>
-    <t>Permission ton tai.</t>
-  </si>
-  <si>
-    <t>1.Sua Permission 2.Luu</t>
-  </si>
-  <si>
-    <t>Du lieu moi</t>
-  </si>
-  <si>
-    <t>Permission duoc UPDATE.</t>
-  </si>
-  <si>
-    <t>TC_FR97_ASSIGN</t>
-  </si>
-  <si>
-    <t>[Positive] Gan Permission cho Role (FR97)</t>
-  </si>
-  <si>
-    <t>[Positive] Gan Permission cho Role</t>
-  </si>
-  <si>
-    <t>Role va Permission ton tai.</t>
-  </si>
-  <si>
-    <t>1.Chon Role 2.Assign Permission</t>
-  </si>
-  <si>
-    <t>Role + Permission</t>
-  </si>
-  <si>
-    <t>Permission duoc gan cho Role.</t>
-  </si>
-  <si>
-    <t>TC_FR99_CHECK</t>
-  </si>
-  <si>
-    <t>[Positive] Backend kiem tra Permission (FR99)</t>
-  </si>
-  <si>
-    <t>[Positive] Backend kiem tra Permission</t>
-  </si>
-  <si>
-    <t>User co permission hop le.</t>
-  </si>
-  <si>
-    <t>1.Gui request can permission</t>
-  </si>
-  <si>
-    <t>Backend cho phep request.</t>
-  </si>
-  <si>
-    <t>High (NFR02) (BRULE23, BRULE24)</t>
-  </si>
-  <si>
-    <t>TC_FR100_DENY</t>
-  </si>
-  <si>
-    <t>[Negative] Chan truy cap trai quyen (FR100)</t>
-  </si>
-  <si>
-    <t>[Negative] Chan truy cap trai quyen</t>
-  </si>
-  <si>
-    <t>1.Gui request admin</t>
-  </si>
-  <si>
-    <t>Permission thieu</t>
-  </si>
-  <si>
-    <t>Backend reject/403, khong tin permission tu frontend.</t>
-  </si>
-  <si>
-    <t>TC_LOG_AUTHZ_FAIL</t>
-  </si>
-  <si>
-    <t>[Negative] Ghi log authorization failure khi bi tu choi (FR100)</t>
-  </si>
-  <si>
-    <t>[Negative] Ghi log authorization failure khi bi tu choi</t>
-  </si>
-  <si>
-    <t>User thieu permission.</t>
-  </si>
-  <si>
-    <t>1.Gui request trai quyen 2.Kiem tra log</t>
-  </si>
-  <si>
-    <t>He thong reject/403 va ghi log authorization failure.</t>
-  </si>
-  <si>
-    <t>UC37 - Xem AuditLog</t>
-  </si>
-  <si>
-    <t>TC_FR101_POS</t>
-  </si>
-  <si>
-    <t>[Positive] Ghi AuditLog khi Login theo chinh sach (FR101)</t>
-  </si>
-  <si>
-    <t>[Positive] Ghi AuditLog khi Login theo chinh sach</t>
-  </si>
-  <si>
-    <t>User login; chinh sach AuditLog ap dung.</t>
-  </si>
-  <si>
-    <t>1.Login 2.Kiem tra AuditLog</t>
-  </si>
-  <si>
-    <t>Login event</t>
-  </si>
-  <si>
-    <t>AuditLog ghi actor/action/target/timestamp/details phu hop.</t>
-  </si>
-  <si>
-    <t>TC_FR102_POS</t>
-  </si>
-  <si>
-    <t>[Positive] Ghi AuditLog khi thay doi Role (FR102)</t>
-  </si>
-  <si>
-    <t>[Positive] Ghi AuditLog khi thay doi Role</t>
-  </si>
-  <si>
-    <t>Admin thay doi Role.</t>
-  </si>
-  <si>
-    <t>1.Update/assign Role 2.Kiem tra log</t>
-  </si>
-  <si>
-    <t>Role change</t>
-  </si>
-  <si>
-    <t>AuditLog duoc ghi.</t>
-  </si>
-  <si>
-    <t>TC_FR103_POS</t>
-  </si>
-  <si>
-    <t>[Positive] Ghi AuditLog khi thay doi Permission (FR103)</t>
-  </si>
-  <si>
-    <t>[Positive] Ghi AuditLog khi thay doi Permission</t>
-  </si>
-  <si>
-    <t>Admin thay doi Permission.</t>
-  </si>
-  <si>
-    <t>1.Update/assign Permission 2.Kiem tra log</t>
-  </si>
-  <si>
-    <t>Permission change</t>
-  </si>
-  <si>
-    <t>TC_FR104_POS</t>
-  </si>
-  <si>
-    <t>[Positive] Ghi AuditLog khi lock/unlock Account (FR104)</t>
-  </si>
-  <si>
-    <t>[Positive] Ghi AuditLog khi lock/unlock Account</t>
-  </si>
-  <si>
-    <t>Admin co quyen.</t>
-  </si>
-  <si>
-    <t>1.Lock/Unlock 2.Kiem tra log</t>
-  </si>
-  <si>
-    <t>Account status change</t>
-  </si>
-  <si>
-    <t>TC_FR105_POS</t>
-  </si>
-  <si>
-    <t>[Positive] Ghi AuditLog thao tac quan tri quan trong (FR105)</t>
-  </si>
-  <si>
-    <t>[Positive] Ghi AuditLog thao tac quan tri quan trong</t>
-  </si>
-  <si>
-    <t>Admin thuc hien thao tac nhay cam.</t>
-  </si>
-  <si>
-    <t>1.Thuc hien action 2.Kiem tra log</t>
-  </si>
-  <si>
-    <t>Admin action</t>
-  </si>
-  <si>
-    <t>TC_FR105_NOEDIT</t>
-  </si>
-  <si>
-    <t>[Negative] Khong cho sua AuditLog qua UI thong thuong (FR105)</t>
-  </si>
-  <si>
-    <t>[Negative] Khong cho sua AuditLog qua UI thong thuong</t>
-  </si>
-  <si>
-    <t>AuditLog ton tai.</t>
-  </si>
-  <si>
-    <t>1.Mo AuditLog 2.Tim thao tac Edit</t>
-  </si>
-  <si>
-    <t>AuditLog record</t>
-  </si>
-  <si>
-    <t>UI khong cung cap thao tac sua AuditLog.</t>
-  </si>
-  <si>
-    <t>TC_AUDIT_EMPTY</t>
-  </si>
-  <si>
-    <t>[Exception] Xem AuditLog khi chua co ban ghi nao (UC37)</t>
-  </si>
-  <si>
-    <t>[Exception] Xem AuditLog khi chua co ban ghi nao</t>
-  </si>
-  <si>
-    <t>Admin dang nhap; he thong chua ghi AuditLog nao.</t>
-  </si>
-  <si>
-    <t>1.Goi API xem danh sach AuditLog</t>
-  </si>
-  <si>
-    <t>Chua co AuditLog nao</t>
-  </si>
-  <si>
-    <t>UC38 - Dashboard</t>
-  </si>
-  <si>
-    <t>TC_FR106_107_108_109_110_POS</t>
-  </si>
-  <si>
-    <t>[Positive] Xem Dashboard voi cac chi so tong hop (FR106,107,108,109,110)</t>
-  </si>
-  <si>
-    <t>[Positive] Xem Dashboard voi cac chi so tong hop</t>
-  </si>
-  <si>
-    <t>Management User co quyen; co domain data.</t>
-  </si>
-  <si>
-    <t>1.Mo Dashboard</t>
-  </si>
-  <si>
-    <t>Trip, Payment, Driver, Rating data</t>
-  </si>
-  <si>
-    <t>Hien thi Total Trips, Completed, Cancelled, Revenue, Completion Rate, Cancellation Rate, Driver Metrics.</t>
-  </si>
-  <si>
-    <t>TC_FR106_EMPTY</t>
-  </si>
-  <si>
-    <t>[Exception] Dashboard khi khong co Trip trong pham vi (FR106,108,109)</t>
-  </si>
-  <si>
-    <t>[Exception] Dashboard khi khong co Trip trong pham vi</t>
-  </si>
-  <si>
-    <t>Khong co Trip trong time range.</t>
-  </si>
-  <si>
-    <t>Khong co Trip</t>
-  </si>
-  <si>
-    <t>Khong hien thi so lieu gia; cac chi so phu hop voi tap du lieu rong.</t>
-  </si>
-  <si>
-    <t>TC_FR110_INCOMPLETE</t>
-  </si>
-  <si>
-    <t>[Exception] Driver Metrics thieu du lieu (FR110)</t>
-  </si>
-  <si>
-    <t>[Exception] Driver Metrics thieu du lieu</t>
-  </si>
-  <si>
-    <t>Mot Driver thieu du lieu rating/trip.</t>
-  </si>
-  <si>
-    <t>Du lieu Driver khong day du</t>
-  </si>
-  <si>
-    <t>Chi so khong tinh duoc hien thi N/A/khong du du lieu.</t>
-  </si>
-  <si>
-    <t>TC_FR106_DENY</t>
-  </si>
-  <si>
-    <t>[Negative] User khong phai Management xem Dashboard bi tu choi (FR106)</t>
-  </si>
-  <si>
-    <t>[Negative] User khong phai Management xem Dashboard bi tu choi</t>
+    <t>UC39 - Bao cao Trip</t>
+  </si>
+  <si>
+    <t>TC_FR106_111_POS</t>
+  </si>
+  <si>
+    <t>[Positive] Bao cao Trip theo khoang thoi gian (FR106,111)</t>
+  </si>
+  <si>
+    <t>[Positive] Bao cao Trip theo khoang thoi gian</t>
+  </si>
+  <si>
+    <t>Management User co quyen.</t>
+  </si>
+  <si>
+    <t>1.Chon From Date 2.Chon To Date 3.Xem report</t>
+  </si>
+  <si>
+    <t>Khoang thoi gian hop le</t>
+  </si>
+  <si>
+    <t>Bao cao COUNT(Trip) dung trong khoang thoi gian.</t>
+  </si>
+  <si>
+    <t>High (BRULE27)</t>
+  </si>
+  <si>
+    <t>TC_FR111_STATUS</t>
+  </si>
+  <si>
+    <t>[Positive] Loc bao cao Trip theo status (FR111)</t>
+  </si>
+  <si>
+    <t>[Positive] Loc bao cao Trip theo status</t>
+  </si>
+  <si>
+    <t>Co Trip nhieu status.</t>
+  </si>
+  <si>
+    <t>1.Chon status filter</t>
+  </si>
+  <si>
+    <t>Status COMPLETED/CANCELLED</t>
+  </si>
+  <si>
+    <t>Bao cao chi tinh Trip khop filter.</t>
+  </si>
+  <si>
+    <t>TC_FR111_INVALID</t>
+  </si>
+  <si>
+    <t>[Negative] Khoang thoi gian khong hop le (FR111)</t>
+  </si>
+  <si>
+    <t>[Negative] Khoang thoi gian khong hop le</t>
+  </si>
+  <si>
+    <t>1.Chon khoang thoi gian khong hop le</t>
+  </si>
+  <si>
+    <t>From/To khong hop le</t>
+  </si>
+  <si>
+    <t>He thong yeu cau dieu chinh filter va khong tra so lieu sai.</t>
+  </si>
+  <si>
+    <t>TC_FR112_DETAIL</t>
+  </si>
+  <si>
+    <t>[Positive] Xem du lieu chi tiet cua bao cao (FR112)</t>
+  </si>
+  <si>
+    <t>[Positive] Xem du lieu chi tiet cua bao cao</t>
+  </si>
+  <si>
+    <t>Bao cao co du lieu.</t>
+  </si>
+  <si>
+    <t>1.Chon chi so/ban ghi chi tiet</t>
+  </si>
+  <si>
+    <t>He thong hien thi du lieu nguon trong pham vi quyen.</t>
+  </si>
+  <si>
+    <t>TC_FR106_AGG</t>
+  </si>
+  <si>
+    <t>[Positive] Bao cao dung aggregation thay vi load toan bo record (FR106,111)</t>
+  </si>
+  <si>
+    <t>[Positive] Bao cao dung aggregation thay vi load toan bo record</t>
+  </si>
+  <si>
+    <t>Co tap du lieu lon.</t>
+  </si>
+  <si>
+    <t>1.Thuc hien report 2.Kiem tra query implementation</t>
+  </si>
+  <si>
+    <t>Tap du lieu lon</t>
+  </si>
+  <si>
+    <t>Report su dung aggregation query phu hop, khong load toan bo record vao application (NFR11).</t>
+  </si>
+  <si>
+    <t>TC_FR111_DENY</t>
+  </si>
+  <si>
+    <t>[Negative] User khong phai Management xem Bao cao Trip bi tu choi (FR111)</t>
+  </si>
+  <si>
+    <t>[Negative] User khong phai Management xem Bao cao Trip bi tu choi</t>
   </si>
   <si>
     <t>User dang nhap khong co role Management.</t>
   </si>
   <si>
-    <t>1.Yeu cau xem Dashboard</t>
+    <t>1.Yeu cau xem Bao cao Trip</t>
   </si>
   <si>
     <t>User khong co permission Management</t>
   </si>
   <si>
-    <t>He thong reject/403; khong tra ve du lieu Dashboard.</t>
+    <t>He thong reject/403; khong tra ve du lieu bao cao.</t>
   </si>
   <si>
     <t>High (NFR02, BRULE23)</t>
   </si>
   <si>
-    <t>UC39 - Bao cao Trip</t>
-  </si>
-  <si>
-    <t>TC_FR106_111_POS</t>
-  </si>
-  <si>
-    <t>[Positive] Bao cao Trip theo khoang thoi gian (FR106,111)</t>
-  </si>
-  <si>
-    <t>[Positive] Bao cao Trip theo khoang thoi gian</t>
-  </si>
-  <si>
-    <t>Management User co quyen.</t>
-  </si>
-  <si>
-    <t>1.Chon From Date 2.Chon To Date 3.Xem report</t>
-  </si>
-  <si>
-    <t>Khoang thoi gian hop le</t>
-  </si>
-  <si>
-    <t>Bao cao COUNT(Trip) dung trong khoang thoi gian.</t>
-  </si>
-  <si>
-    <t>High (BRULE27)</t>
-  </si>
-  <si>
-    <t>TC_FR111_STATUS</t>
-  </si>
-  <si>
-    <t>[Positive] Loc bao cao Trip theo status (FR111)</t>
-  </si>
-  <si>
-    <t>[Positive] Loc bao cao Trip theo status</t>
-  </si>
-  <si>
-    <t>Co Trip nhieu status.</t>
-  </si>
-  <si>
-    <t>1.Chon status filter</t>
-  </si>
-  <si>
-    <t>Status COMPLETED/CANCELLED</t>
-  </si>
-  <si>
-    <t>Bao cao chi tinh Trip khop filter.</t>
-  </si>
-  <si>
-    <t>TC_FR111_INVALID</t>
-  </si>
-  <si>
-    <t>[Negative] Khoang thoi gian khong hop le (FR111)</t>
-  </si>
-  <si>
-    <t>[Negative] Khoang thoi gian khong hop le</t>
-  </si>
-  <si>
-    <t>1.Chon khoang thoi gian khong hop le</t>
-  </si>
-  <si>
-    <t>From/To khong hop le</t>
-  </si>
-  <si>
-    <t>He thong yeu cau dieu chinh filter va khong tra so lieu sai.</t>
-  </si>
-  <si>
-    <t>TC_FR112_DETAIL</t>
-  </si>
-  <si>
-    <t>[Positive] Xem du lieu chi tiet cua bao cao (FR112)</t>
-  </si>
-  <si>
-    <t>[Positive] Xem du lieu chi tiet cua bao cao</t>
-  </si>
-  <si>
-    <t>Bao cao co du lieu.</t>
-  </si>
-  <si>
-    <t>1.Chon chi so/ban ghi chi tiet</t>
-  </si>
-  <si>
-    <t>He thong hien thi du lieu nguon trong pham vi quyen.</t>
-  </si>
-  <si>
-    <t>TC_FR106_AGG</t>
-  </si>
-  <si>
-    <t>[Positive] Bao cao dung aggregation thay vi load toan bo record (FR106,111)</t>
-  </si>
-  <si>
-    <t>[Positive] Bao cao dung aggregation thay vi load toan bo record</t>
-  </si>
-  <si>
-    <t>Co tap du lieu lon.</t>
-  </si>
-  <si>
-    <t>1.Thuc hien report 2.Kiem tra query implementation</t>
-  </si>
-  <si>
-    <t>Tap du lieu lon</t>
-  </si>
-  <si>
-    <t>Report su dung aggregation query phu hop, khong load toan bo record vao application (NFR11).</t>
-  </si>
-  <si>
-    <t>TC_FR111_DENY</t>
-  </si>
-  <si>
-    <t>[Negative] User khong phai Management xem Bao cao Trip bi tu choi (FR111)</t>
-  </si>
-  <si>
-    <t>[Negative] User khong phai Management xem Bao cao Trip bi tu choi</t>
-  </si>
-  <si>
-    <t>1.Yeu cau xem Bao cao Trip</t>
-  </si>
-  <si>
-    <t>He thong reject/403; khong tra ve du lieu bao cao.</t>
+    <t>TC_FR108_RATE</t>
+  </si>
+  <si>
+    <t>[Positive] Bao cao ty le hoan thanh Trip (FR108)</t>
+  </si>
+  <si>
+    <t>[Positive] Bao cao ty le hoan thanh Trip</t>
+  </si>
+  <si>
+    <t>Co du lieu Trip trong khoang thoi gian bao cao.</t>
+  </si>
+  <si>
+    <t>1.Goi API bao cao Trip 2.Kiem tra ty le hoan thanh</t>
+  </si>
+  <si>
+    <t>Trip voi nhieu status khac nhau</t>
+  </si>
+  <si>
+    <t>He thong tra ve dung ty le Trip COMPLETED / tong so Trip trong khoang thoi gian.</t>
+  </si>
+  <si>
+    <t>Medium (FR108)</t>
+  </si>
+  <si>
+    <t>TC_FR109_RATE</t>
+  </si>
+  <si>
+    <t>[Positive] Bao cao ty le huy Trip (FR109)</t>
+  </si>
+  <si>
+    <t>[Positive] Bao cao ty le huy Trip</t>
+  </si>
+  <si>
+    <t>1.Goi API bao cao Trip 2.Kiem tra ty le huy</t>
+  </si>
+  <si>
+    <t>He thong tra ve dung ty le Trip CANCELLED / tong so Trip trong khoang thoi gian.</t>
+  </si>
+  <si>
+    <t>Medium (FR109)</t>
   </si>
   <si>
     <t>UC40 - Bao cao doanh thu</t>
@@ -4457,25 +4241,25 @@
     <t>He thong reject/403; khong tra ve du lieu.</t>
   </si>
   <si>
+    <t>[Missing Data] Dang ky thieu  email (FR1)</t>
+  </si>
+  <si>
+    <t>[Missing Data] Dang ky thieu email</t>
+  </si>
+  <si>
+    <t>1.Nhap fullName/password, bo trong email 2.Gui dang ky</t>
+  </si>
+  <si>
+    <t>email rong</t>
+  </si>
+  <si>
     <t>[Missing Data] Dang ky thieu phone (FR1)</t>
   </si>
   <si>
     <t>[Missing Data] Dang ky thieu phone</t>
   </si>
   <si>
-    <t>[Missing Data] Dang ky thieu email</t>
-  </si>
-  <si>
-    <t>[Missing Data] Dang ky thieu  email (FR1)</t>
-  </si>
-  <si>
     <t>1.Nhap fullName/password, bo trong phone 2.Gui dang ky</t>
-  </si>
-  <si>
-    <t>1.Nhap fullName/password, bo trong email 2.Gui dang ky</t>
-  </si>
-  <si>
-    <t>email rong</t>
   </si>
   <si>
     <t>phone rong</t>
@@ -4498,16 +4282,19 @@
       <sz val="13"/>
       <color rgb="FF1F4E78"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -5146,19 +4933,19 @@
         <v>62</v>
       </c>
       <c r="B11" t="s">
-        <v>1468</v>
+        <v>1394</v>
       </c>
       <c r="C11" t="s">
-        <v>1467</v>
+        <v>1395</v>
       </c>
       <c r="D11" t="s">
         <v>12</v>
       </c>
       <c r="E11" t="s">
-        <v>1470</v>
+        <v>1396</v>
       </c>
       <c r="F11" t="s">
-        <v>1471</v>
+        <v>1397</v>
       </c>
       <c r="G11" t="s">
         <v>63</v>
@@ -5172,19 +4959,19 @@
         <v>62</v>
       </c>
       <c r="B12" t="s">
-        <v>1465</v>
+        <v>1398</v>
       </c>
       <c r="C12" t="s">
-        <v>1466</v>
+        <v>1399</v>
       </c>
       <c r="D12" t="s">
         <v>12</v>
       </c>
       <c r="E12" t="s">
-        <v>1469</v>
+        <v>1400</v>
       </c>
       <c r="F12" t="s">
-        <v>1472</v>
+        <v>1401</v>
       </c>
       <c r="G12" t="s">
         <v>63</v>
@@ -8962,7 +8749,7 @@
 
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1B00-000000000000}">
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -9024,16 +8811,16 @@
         <v>944</v>
       </c>
       <c r="D3" s="3" t="s">
+        <v>891</v>
+      </c>
+      <c r="E3" s="3" t="s">
         <v>945</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="F3" s="4" t="s">
         <v>946</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="G3" s="3" t="s">
         <v>947</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>948</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>16</v>
@@ -9041,27 +8828,131 @@
     </row>
     <row r="4" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
+        <v>948</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>949</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="C4" s="3" t="s">
         <v>950</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="D4" s="3" t="s">
         <v>951</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="E4" s="3" t="s">
         <v>952</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="F4" s="4" t="s">
         <v>953</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="G4" s="3" t="s">
         <v>954</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="H4" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="2" t="s">
         <v>955</v>
       </c>
-      <c r="H4" s="3" t="s">
+      <c r="B5" s="3" t="s">
+        <v>956</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>957</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>958</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>959</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>960</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>961</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="2" t="s">
+        <v>962</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>963</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>964</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>891</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>965</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>966</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>967</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="2" t="s">
+        <v>968</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>969</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>970</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>971</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>945</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>899</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>375</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>972</v>
+      </c>
+      <c r="B8" t="s">
+        <v>973</v>
+      </c>
+      <c r="C8" t="s">
+        <v>974</v>
+      </c>
+      <c r="D8" t="s">
+        <v>975</v>
+      </c>
+      <c r="E8" t="s">
+        <v>976</v>
+      </c>
+      <c r="F8" t="s">
+        <v>977</v>
+      </c>
+      <c r="G8" t="s">
+        <v>978</v>
+      </c>
+      <c r="H8" t="s">
         <v>55</v>
       </c>
     </row>
@@ -9075,7 +8966,7 @@
 
 <file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1C00-000000000000}">
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -9090,7 +8981,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
-        <v>956</v>
+        <v>979</v>
       </c>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
@@ -9128,25 +9019,25 @@
     </row>
     <row r="3" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>957</v>
+        <v>980</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>958</v>
+        <v>981</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>959</v>
+        <v>982</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>891</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>960</v>
+        <v>983</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>961</v>
+        <v>984</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>962</v>
+        <v>985</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>16</v>
@@ -9154,25 +9045,25 @@
     </row>
     <row r="4" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>963</v>
+        <v>986</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>964</v>
+        <v>987</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>965</v>
+        <v>988</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>966</v>
+        <v>989</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>967</v>
+        <v>990</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>968</v>
+        <v>953</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>969</v>
+        <v>991</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>16</v>
@@ -9180,25 +9071,25 @@
     </row>
     <row r="5" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
-        <v>970</v>
+        <v>992</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>971</v>
+        <v>993</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>972</v>
+        <v>994</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>973</v>
+        <v>995</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>974</v>
+        <v>959</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>975</v>
+        <v>960</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>976</v>
+        <v>991</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>16</v>
@@ -9206,25 +9097,25 @@
     </row>
     <row r="6" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>977</v>
+        <v>996</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>978</v>
+        <v>997</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>979</v>
+        <v>998</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>980</v>
+        <v>891</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>981</v>
+        <v>999</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>899</v>
+        <v>1000</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>982</v>
+        <v>1001</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>16</v>
@@ -9232,80 +9123,54 @@
     </row>
     <row r="7" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
-        <v>983</v>
+        <v>1002</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>984</v>
+        <v>1003</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>985</v>
+        <v>1004</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>891</v>
+        <v>971</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>986</v>
+        <v>1005</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>987</v>
+        <v>1006</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>988</v>
+        <v>375</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="2" t="s">
-        <v>989</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>990</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>991</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>992</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>993</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>994</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>995</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>996</v>
-      </c>
-      <c r="B9" t="s">
-        <v>997</v>
-      </c>
-      <c r="C9" t="s">
-        <v>998</v>
-      </c>
-      <c r="D9" t="s">
-        <v>999</v>
-      </c>
-      <c r="E9" t="s">
-        <v>1000</v>
-      </c>
-      <c r="F9" t="s">
-        <v>1001</v>
-      </c>
-      <c r="G9" t="s">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>1007</v>
+      </c>
+      <c r="B8" t="s">
+        <v>1008</v>
+      </c>
+      <c r="C8" t="s">
+        <v>1009</v>
+      </c>
+      <c r="D8" t="s">
+        <v>1010</v>
+      </c>
+      <c r="E8" t="s">
+        <v>1011</v>
+      </c>
+      <c r="F8" t="s">
+        <v>977</v>
+      </c>
+      <c r="G8" t="s">
         <v>360</v>
       </c>
-      <c r="H9" t="s">
-        <v>1002</v>
+      <c r="H8" t="s">
+        <v>55</v>
       </c>
     </row>
   </sheetData>
@@ -9446,7 +9311,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
-        <v>1003</v>
+        <v>1012</v>
       </c>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
@@ -9484,25 +9349,25 @@
     </row>
     <row r="3" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>1004</v>
+        <v>1013</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>1005</v>
+        <v>1014</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>1006</v>
+        <v>1015</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>891</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>1007</v>
+        <v>1016</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>1008</v>
+        <v>1017</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>1009</v>
+        <v>1018</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>16</v>
@@ -9510,25 +9375,25 @@
     </row>
     <row r="4" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>1010</v>
+        <v>1019</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>1011</v>
+        <v>1020</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>1012</v>
+        <v>1021</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>1013</v>
+        <v>1022</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>1014</v>
+        <v>990</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>1015</v>
+        <v>1023</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>1016</v>
+        <v>1024</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>16</v>
@@ -9536,25 +9401,25 @@
     </row>
     <row r="5" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
-        <v>1017</v>
+        <v>1025</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>1018</v>
+        <v>1026</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>1019</v>
+        <v>1027</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>1020</v>
+        <v>1028</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>1021</v>
+        <v>1029</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>1022</v>
+        <v>1030</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>16</v>
@@ -9562,25 +9427,25 @@
     </row>
     <row r="6" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>1024</v>
+        <v>1031</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>1025</v>
+        <v>1032</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>1026</v>
+        <v>1033</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>891</v>
+        <v>1034</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>1027</v>
+        <v>1035</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>1028</v>
+        <v>1036</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>1029</v>
+        <v>1037</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>16</v>
@@ -9588,22 +9453,22 @@
     </row>
     <row r="7" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
-        <v>1030</v>
+        <v>1038</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>1031</v>
+        <v>1039</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>1032</v>
+        <v>1040</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>980</v>
+        <v>971</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>1007</v>
+        <v>1041</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>899</v>
+        <v>1006</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>375</v>
@@ -9614,25 +9479,25 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>1033</v>
+        <v>1042</v>
       </c>
       <c r="B8" t="s">
-        <v>1034</v>
+        <v>1043</v>
       </c>
       <c r="C8" t="s">
-        <v>1035</v>
+        <v>1044</v>
       </c>
       <c r="D8" t="s">
-        <v>1036</v>
+        <v>1045</v>
       </c>
       <c r="E8" t="s">
-        <v>1037</v>
+        <v>1046</v>
       </c>
       <c r="F8" t="s">
-        <v>1038</v>
+        <v>977</v>
       </c>
       <c r="G8" t="s">
-        <v>1039</v>
+        <v>360</v>
       </c>
       <c r="H8" t="s">
         <v>55</v>
@@ -9648,440 +9513,6 @@
 
 <file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1E00-000000000000}">
-  <dimension ref="A1:H8"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="18" customWidth="1"/>
-    <col min="2" max="2" width="26" customWidth="1"/>
-    <col min="3" max="3" width="30" customWidth="1"/>
-    <col min="4" max="4" width="26" customWidth="1"/>
-    <col min="5" max="5" width="34" customWidth="1"/>
-    <col min="6" max="6" width="26" customWidth="1"/>
-    <col min="7" max="7" width="36" customWidth="1"/>
-    <col min="8" max="8" width="10" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="5" t="s">
-        <v>1040</v>
-      </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-    </row>
-    <row r="2" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="2" t="s">
-        <v>1041</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>1042</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>1043</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>891</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>1044</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>1045</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>1046</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="2" t="s">
-        <v>1047</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>1048</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>1049</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>1050</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>1051</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>1015</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>1052</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="2" t="s">
-        <v>1053</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>1054</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>1055</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>1056</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>1021</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>1022</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>1052</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="2" t="s">
-        <v>1057</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>1058</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>1059</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>891</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>1060</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>1061</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>1062</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="2" t="s">
-        <v>1063</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>1064</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>1065</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>980</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>1066</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>1067</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>375</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>1068</v>
-      </c>
-      <c r="B8" t="s">
-        <v>1069</v>
-      </c>
-      <c r="C8" t="s">
-        <v>1070</v>
-      </c>
-      <c r="D8" t="s">
-        <v>1071</v>
-      </c>
-      <c r="E8" t="s">
-        <v>1072</v>
-      </c>
-      <c r="F8" t="s">
-        <v>1038</v>
-      </c>
-      <c r="G8" t="s">
-        <v>360</v>
-      </c>
-      <c r="H8" t="s">
-        <v>55</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:H1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1F00-000000000000}">
-  <dimension ref="A1:H8"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="18" customWidth="1"/>
-    <col min="2" max="2" width="26" customWidth="1"/>
-    <col min="3" max="3" width="30" customWidth="1"/>
-    <col min="4" max="4" width="26" customWidth="1"/>
-    <col min="5" max="5" width="34" customWidth="1"/>
-    <col min="6" max="6" width="26" customWidth="1"/>
-    <col min="7" max="7" width="36" customWidth="1"/>
-    <col min="8" max="8" width="10" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="5" t="s">
-        <v>1073</v>
-      </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-    </row>
-    <row r="2" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="2" t="s">
-        <v>1074</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>1075</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>1076</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>891</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>1077</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>1078</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>1079</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="2" t="s">
-        <v>1080</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>1081</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>1082</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>1083</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>1051</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>1084</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>1085</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="2" t="s">
-        <v>1086</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>1087</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>1088</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>1089</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>1090</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>1091</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>1085</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="2" t="s">
-        <v>1092</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>1093</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>1094</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>1095</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>1096</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>1097</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>1098</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="2" t="s">
-        <v>1099</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>1100</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>1101</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>980</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>1102</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>1067</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>375</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>1103</v>
-      </c>
-      <c r="B8" t="s">
-        <v>1104</v>
-      </c>
-      <c r="C8" t="s">
-        <v>1105</v>
-      </c>
-      <c r="D8" t="s">
-        <v>1106</v>
-      </c>
-      <c r="E8" t="s">
-        <v>1107</v>
-      </c>
-      <c r="F8" t="s">
-        <v>1038</v>
-      </c>
-      <c r="G8" t="s">
-        <v>360</v>
-      </c>
-      <c r="H8" t="s">
-        <v>55</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:H1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2000-000000000000}">
   <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
@@ -10097,7 +9528,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
-        <v>1108</v>
+        <v>1047</v>
       </c>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
@@ -10135,25 +9566,25 @@
     </row>
     <row r="3" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>1109</v>
+        <v>1048</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>1110</v>
+        <v>1049</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>1111</v>
+        <v>1050</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>891</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>1112</v>
+        <v>1051</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>1113</v>
+        <v>1052</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>1114</v>
+        <v>1053</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>16</v>
@@ -10161,25 +9592,25 @@
     </row>
     <row r="4" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>1115</v>
+        <v>1054</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>1116</v>
+        <v>1055</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>1117</v>
+        <v>1056</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>891</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>1118</v>
+        <v>1057</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>1119</v>
+        <v>1058</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>1120</v>
+        <v>1059</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>16</v>
@@ -10187,25 +9618,25 @@
     </row>
     <row r="5" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
-        <v>1121</v>
+        <v>1060</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>1122</v>
+        <v>1061</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>1123</v>
+        <v>1062</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>891</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>1124</v>
+        <v>1063</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>1125</v>
+        <v>1064</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>1126</v>
+        <v>1065</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>16</v>
@@ -10213,25 +9644,25 @@
     </row>
     <row r="6" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>1127</v>
+        <v>1066</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>1128</v>
+        <v>1067</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>1129</v>
+        <v>1068</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>1130</v>
+        <v>1069</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>1131</v>
+        <v>1070</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>1132</v>
+        <v>1071</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>1133</v>
+        <v>1072</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>16</v>
@@ -10239,22 +9670,22 @@
     </row>
     <row r="7" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
-        <v>1134</v>
+        <v>1073</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>1135</v>
+        <v>1074</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>1136</v>
+        <v>1075</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>980</v>
+        <v>971</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>1112</v>
+        <v>1051</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>1067</v>
+        <v>1006</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>375</v>
@@ -10265,25 +9696,25 @@
     </row>
     <row r="8" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
-        <v>1137</v>
+        <v>1076</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>1138</v>
+        <v>1077</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>1139</v>
+        <v>1078</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>1140</v>
+        <v>1079</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>1141</v>
+        <v>1080</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>1142</v>
+        <v>1081</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>1143</v>
+        <v>1082</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>16</v>
@@ -10291,25 +9722,25 @@
     </row>
     <row r="9" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
-        <v>1144</v>
+        <v>1083</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>1145</v>
+        <v>1084</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>1146</v>
+        <v>1085</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>1147</v>
+        <v>1086</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>1148</v>
+        <v>1087</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>1149</v>
+        <v>1088</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>1150</v>
+        <v>1089</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>16</v>
@@ -10317,25 +9748,25 @@
     </row>
     <row r="10" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
-        <v>1151</v>
+        <v>1090</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>1152</v>
+        <v>1091</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>1153</v>
+        <v>1092</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>1154</v>
+        <v>1093</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>1155</v>
+        <v>1094</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>1156</v>
+        <v>1095</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>1157</v>
+        <v>1096</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>55</v>
@@ -10343,22 +9774,22 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>1158</v>
+        <v>1097</v>
       </c>
       <c r="B11" t="s">
-        <v>1159</v>
+        <v>1098</v>
       </c>
       <c r="C11" t="s">
-        <v>1160</v>
+        <v>1099</v>
       </c>
       <c r="D11" t="s">
-        <v>1161</v>
+        <v>1100</v>
       </c>
       <c r="E11" t="s">
-        <v>1162</v>
+        <v>1101</v>
       </c>
       <c r="F11" t="s">
-        <v>1163</v>
+        <v>1102</v>
       </c>
       <c r="G11" t="s">
         <v>360</v>
@@ -10375,8 +9806,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2100-000000000000}">
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1F00-000000000000}">
   <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
@@ -10392,7 +9823,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
-        <v>1164</v>
+        <v>1103</v>
       </c>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
@@ -10430,25 +9861,25 @@
     </row>
     <row r="3" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>1165</v>
+        <v>1104</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>1166</v>
+        <v>1105</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>1167</v>
+        <v>1106</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>1168</v>
+        <v>1107</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>1169</v>
+        <v>1108</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>1170</v>
+        <v>1109</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>1171</v>
+        <v>1110</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>146</v>
@@ -10456,51 +9887,51 @@
     </row>
     <row r="4" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>1172</v>
+        <v>1111</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>1173</v>
+        <v>1112</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>1174</v>
+        <v>1113</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>1175</v>
+        <v>1114</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>1176</v>
+        <v>1115</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>1177</v>
+        <v>1116</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>1178</v>
+        <v>1117</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>1179</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
-        <v>1180</v>
+        <v>1119</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>1181</v>
+        <v>1120</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>1182</v>
+        <v>1121</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>1183</v>
+        <v>1122</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>1184</v>
+        <v>1123</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>1185</v>
+        <v>1124</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>1186</v>
+        <v>1125</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>16</v>
@@ -10508,25 +9939,25 @@
     </row>
     <row r="6" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>1187</v>
+        <v>1126</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>1188</v>
+        <v>1127</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>1189</v>
+        <v>1128</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>1190</v>
+        <v>1129</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>1191</v>
+        <v>1130</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>1177</v>
+        <v>1116</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>1192</v>
+        <v>1131</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>16</v>
@@ -10534,25 +9965,25 @@
     </row>
     <row r="7" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
-        <v>1193</v>
+        <v>1132</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>1194</v>
+        <v>1133</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>1195</v>
+        <v>1134</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>1196</v>
+        <v>1135</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>1197</v>
+        <v>1136</v>
       </c>
       <c r="F7" s="4" t="s">
         <v>85</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>1198</v>
+        <v>1137</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>16</v>
@@ -10560,25 +9991,25 @@
     </row>
     <row r="8" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
-        <v>1199</v>
+        <v>1138</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>1200</v>
+        <v>1139</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>1201</v>
+        <v>1140</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>1202</v>
+        <v>1141</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>1203</v>
+        <v>1142</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>1204</v>
+        <v>1143</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>1205</v>
+        <v>1144</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>16</v>
@@ -10586,25 +10017,25 @@
     </row>
     <row r="9" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
-        <v>1206</v>
+        <v>1145</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>1207</v>
+        <v>1146</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>1208</v>
+        <v>1147</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>1209</v>
+        <v>1148</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>1210</v>
+        <v>1149</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>1067</v>
+        <v>1006</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>1211</v>
+        <v>1150</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>16</v>
@@ -10612,28 +10043,28 @@
     </row>
     <row r="10" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
-        <v>1212</v>
+        <v>1151</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>1213</v>
+        <v>1152</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>1214</v>
+        <v>1153</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>1215</v>
+        <v>1154</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>1216</v>
+        <v>1155</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>1217</v>
+        <v>1156</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>1218</v>
+        <v>1157</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>1219</v>
+        <v>1158</v>
       </c>
     </row>
   </sheetData>
@@ -10644,8 +10075,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2200-000000000000}">
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2000-000000000000}">
   <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
@@ -10661,7 +10092,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
-        <v>1220</v>
+        <v>1159</v>
       </c>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
@@ -10699,25 +10130,25 @@
     </row>
     <row r="3" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>1221</v>
+        <v>1160</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>1222</v>
+        <v>1161</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>1223</v>
+        <v>1162</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>1224</v>
+        <v>1163</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>1225</v>
+        <v>1164</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>1226</v>
+        <v>1165</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>1227</v>
+        <v>1166</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>16</v>
@@ -10725,25 +10156,25 @@
     </row>
     <row r="4" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>1228</v>
+        <v>1167</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>1229</v>
+        <v>1168</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>1230</v>
+        <v>1169</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>1224</v>
+        <v>1163</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>1231</v>
+        <v>1170</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>1232</v>
+        <v>1171</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>1233</v>
+        <v>1172</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>16</v>
@@ -10751,25 +10182,25 @@
     </row>
     <row r="5" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
-        <v>1234</v>
+        <v>1173</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>1235</v>
+        <v>1174</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>1236</v>
+        <v>1175</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>1237</v>
+        <v>1176</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>1238</v>
+        <v>1177</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>1239</v>
+        <v>1178</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>1240</v>
+        <v>1179</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>16</v>
@@ -10777,25 +10208,25 @@
     </row>
     <row r="6" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>1241</v>
+        <v>1180</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>1242</v>
+        <v>1181</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>1243</v>
+        <v>1182</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>1224</v>
+        <v>1163</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>1244</v>
+        <v>1183</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>1204</v>
+        <v>1143</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>1245</v>
+        <v>1184</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>16</v>
@@ -10803,25 +10234,25 @@
     </row>
     <row r="7" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
-        <v>1246</v>
+        <v>1185</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>1247</v>
+        <v>1186</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>1248</v>
+        <v>1187</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>1249</v>
+        <v>1188</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>1250</v>
+        <v>1189</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>1251</v>
+        <v>1190</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>1252</v>
+        <v>1191</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>16</v>
@@ -10835,8 +10266,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2300-000000000000}">
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2100-000000000000}">
   <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
@@ -10852,7 +10283,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
-        <v>1253</v>
+        <v>1192</v>
       </c>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
@@ -10890,25 +10321,25 @@
     </row>
     <row r="3" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>1254</v>
+        <v>1193</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>1255</v>
+        <v>1194</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>1256</v>
+        <v>1195</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>1224</v>
+        <v>1163</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>1257</v>
+        <v>1196</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>1258</v>
+        <v>1197</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>1259</v>
+        <v>1198</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>16</v>
@@ -10916,25 +10347,25 @@
     </row>
     <row r="4" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>1260</v>
+        <v>1199</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>1261</v>
+        <v>1200</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>1262</v>
+        <v>1201</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>1224</v>
+        <v>1163</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>1263</v>
+        <v>1202</v>
       </c>
       <c r="F4" s="4" t="s">
         <v>346</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>1264</v>
+        <v>1203</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>16</v>
@@ -10942,25 +10373,25 @@
     </row>
     <row r="5" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
-        <v>1265</v>
+        <v>1204</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>1266</v>
+        <v>1205</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>1267</v>
+        <v>1206</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>1268</v>
+        <v>1207</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>1269</v>
+        <v>1208</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>1270</v>
+        <v>1209</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>1271</v>
+        <v>1210</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>16</v>
@@ -10968,25 +10399,25 @@
     </row>
     <row r="6" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>1272</v>
+        <v>1211</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>1273</v>
+        <v>1212</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>1274</v>
+        <v>1213</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>1275</v>
+        <v>1214</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>1276</v>
+        <v>1215</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>1277</v>
+        <v>1216</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>1278</v>
+        <v>1217</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>16</v>
@@ -10994,51 +10425,51 @@
     </row>
     <row r="7" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
-        <v>1279</v>
+        <v>1218</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>1280</v>
+        <v>1219</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>1281</v>
+        <v>1220</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>1282</v>
+        <v>1221</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>1283</v>
+        <v>1222</v>
       </c>
       <c r="F7" s="4" t="s">
         <v>346</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>1284</v>
+        <v>1223</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>1285</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
-        <v>1286</v>
+        <v>1225</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>1287</v>
+        <v>1226</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>1288</v>
+        <v>1227</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>897</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>1289</v>
+        <v>1228</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>1290</v>
+        <v>1229</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>1291</v>
+        <v>1230</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>16</v>
@@ -11046,25 +10477,25 @@
     </row>
     <row r="9" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
-        <v>1292</v>
+        <v>1231</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>1293</v>
+        <v>1232</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>1294</v>
+        <v>1233</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>1295</v>
+        <v>1234</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>1296</v>
+        <v>1235</v>
       </c>
       <c r="F9" s="4" t="s">
         <v>899</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>1297</v>
+        <v>1236</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>16</v>
@@ -11078,8 +10509,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2400-000000000000}">
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2200-000000000000}">
   <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
@@ -11095,7 +10526,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
-        <v>1298</v>
+        <v>1237</v>
       </c>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
@@ -11133,25 +10564,25 @@
     </row>
     <row r="3" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>1299</v>
+        <v>1238</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>1300</v>
+        <v>1239</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>1301</v>
+        <v>1240</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>1302</v>
+        <v>1241</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>1303</v>
+        <v>1242</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>1304</v>
+        <v>1243</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>1305</v>
+        <v>1244</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>16</v>
@@ -11159,51 +10590,51 @@
     </row>
     <row r="4" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>1306</v>
+        <v>1245</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>1307</v>
+        <v>1246</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>1308</v>
+        <v>1247</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>1309</v>
+        <v>1248</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>1310</v>
+        <v>1249</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>1311</v>
+        <v>1250</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>1312</v>
+        <v>1251</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>1179</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
-        <v>1313</v>
+        <v>1252</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>1314</v>
+        <v>1253</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>1315</v>
+        <v>1254</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>1316</v>
+        <v>1255</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>1317</v>
+        <v>1256</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>1318</v>
+        <v>1257</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>1312</v>
+        <v>1251</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>16</v>
@@ -11211,25 +10642,25 @@
     </row>
     <row r="6" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>1319</v>
+        <v>1258</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>1320</v>
+        <v>1259</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>1321</v>
+        <v>1260</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>1322</v>
+        <v>1261</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>1323</v>
+        <v>1262</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>1324</v>
+        <v>1263</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>1312</v>
+        <v>1251</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>16</v>
@@ -11237,25 +10668,25 @@
     </row>
     <row r="7" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
-        <v>1325</v>
+        <v>1264</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>1326</v>
+        <v>1265</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>1327</v>
+        <v>1266</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>1328</v>
+        <v>1267</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>1329</v>
+        <v>1268</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>1330</v>
+        <v>1269</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>1218</v>
+        <v>1157</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>16</v>
@@ -11263,25 +10694,25 @@
     </row>
     <row r="8" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
-        <v>1331</v>
+        <v>1270</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>1332</v>
+        <v>1271</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>1333</v>
+        <v>1272</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>1334</v>
+        <v>1273</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>1335</v>
+        <v>1274</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>1336</v>
+        <v>1275</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>1337</v>
+        <v>1276</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>16</v>
@@ -11289,28 +10720,462 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>1338</v>
+        <v>1277</v>
       </c>
       <c r="B9" t="s">
-        <v>1339</v>
+        <v>1278</v>
       </c>
       <c r="C9" t="s">
-        <v>1340</v>
+        <v>1279</v>
       </c>
       <c r="D9" t="s">
-        <v>1341</v>
+        <v>1280</v>
       </c>
       <c r="E9" t="s">
-        <v>1342</v>
+        <v>1281</v>
       </c>
       <c r="F9" t="s">
-        <v>1343</v>
+        <v>1282</v>
       </c>
       <c r="G9" t="s">
         <v>360</v>
       </c>
       <c r="H9" t="s">
-        <v>1002</v>
+        <v>1283</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2300-000000000000}">
+  <dimension ref="A1:H10"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="18" customWidth="1"/>
+    <col min="2" max="2" width="26" customWidth="1"/>
+    <col min="3" max="3" width="30" customWidth="1"/>
+    <col min="4" max="4" width="26" customWidth="1"/>
+    <col min="5" max="5" width="34" customWidth="1"/>
+    <col min="6" max="6" width="26" customWidth="1"/>
+    <col min="7" max="7" width="36" customWidth="1"/>
+    <col min="8" max="8" width="10" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="5" t="s">
+        <v>1284</v>
+      </c>
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
+      <c r="F1" s="6"/>
+      <c r="G1" s="6"/>
+      <c r="H1" s="6"/>
+    </row>
+    <row r="2" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="2" t="s">
+        <v>1285</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>1286</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>1287</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>1288</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>1289</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>1290</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>1291</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>1292</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="2" t="s">
+        <v>1293</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>1294</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>1295</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>1296</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>1297</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>1298</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>1299</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="2" t="s">
+        <v>1300</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>1301</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>1302</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>1288</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>1303</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>1304</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>1305</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="2" t="s">
+        <v>1306</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>1307</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>1308</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>1309</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>1310</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>1052</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>1311</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="2" t="s">
+        <v>1312</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>1313</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>1314</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>1315</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>1316</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>1317</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>1318</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>1319</v>
+      </c>
+      <c r="B8" t="s">
+        <v>1320</v>
+      </c>
+      <c r="C8" t="s">
+        <v>1321</v>
+      </c>
+      <c r="D8" t="s">
+        <v>1322</v>
+      </c>
+      <c r="E8" t="s">
+        <v>1323</v>
+      </c>
+      <c r="F8" t="s">
+        <v>1324</v>
+      </c>
+      <c r="G8" t="s">
+        <v>1325</v>
+      </c>
+      <c r="H8" t="s">
+        <v>1326</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>1327</v>
+      </c>
+      <c r="B9" t="s">
+        <v>1328</v>
+      </c>
+      <c r="C9" t="s">
+        <v>1329</v>
+      </c>
+      <c r="D9" t="s">
+        <v>1330</v>
+      </c>
+      <c r="E9" t="s">
+        <v>1331</v>
+      </c>
+      <c r="F9" t="s">
+        <v>1332</v>
+      </c>
+      <c r="G9" t="s">
+        <v>1333</v>
+      </c>
+      <c r="H9" t="s">
+        <v>1334</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>1335</v>
+      </c>
+      <c r="B10" t="s">
+        <v>1336</v>
+      </c>
+      <c r="C10" t="s">
+        <v>1337</v>
+      </c>
+      <c r="D10" t="s">
+        <v>1330</v>
+      </c>
+      <c r="E10" t="s">
+        <v>1338</v>
+      </c>
+      <c r="F10" t="s">
+        <v>1332</v>
+      </c>
+      <c r="G10" t="s">
+        <v>1339</v>
+      </c>
+      <c r="H10" t="s">
+        <v>1340</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2400-000000000000}">
+  <dimension ref="A1:H6"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="18" customWidth="1"/>
+    <col min="2" max="2" width="26" customWidth="1"/>
+    <col min="3" max="3" width="30" customWidth="1"/>
+    <col min="4" max="4" width="26" customWidth="1"/>
+    <col min="5" max="5" width="34" customWidth="1"/>
+    <col min="6" max="6" width="26" customWidth="1"/>
+    <col min="7" max="7" width="36" customWidth="1"/>
+    <col min="8" max="8" width="10" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="5" t="s">
+        <v>1341</v>
+      </c>
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
+      <c r="F1" s="6"/>
+      <c r="G1" s="6"/>
+      <c r="H1" s="6"/>
+    </row>
+    <row r="2" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="2" t="s">
+        <v>1342</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>1343</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>1344</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>1345</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>1346</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>1347</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>1348</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>1349</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="2" t="s">
+        <v>1350</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>1351</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>1352</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>1353</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>1354</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>1355</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>1356</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="2" t="s">
+        <v>1357</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>1358</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>1359</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>1360</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>1346</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>1361</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>1362</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>1363</v>
+      </c>
+      <c r="B6" t="s">
+        <v>1364</v>
+      </c>
+      <c r="C6" t="s">
+        <v>1365</v>
+      </c>
+      <c r="D6" t="s">
+        <v>1322</v>
+      </c>
+      <c r="E6" t="s">
+        <v>1366</v>
+      </c>
+      <c r="F6" t="s">
+        <v>1324</v>
+      </c>
+      <c r="G6" t="s">
+        <v>1367</v>
+      </c>
+      <c r="H6" t="s">
+        <v>1326</v>
       </c>
     </row>
   </sheetData>
@@ -11338,7 +11203,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
-        <v>1344</v>
+        <v>1368</v>
       </c>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
@@ -11376,25 +11241,25 @@
     </row>
     <row r="3" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>1345</v>
+        <v>1369</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>1346</v>
+        <v>1370</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>1347</v>
+        <v>1371</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>1348</v>
+        <v>1372</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>1349</v>
+        <v>1373</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>1350</v>
+        <v>1374</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>1351</v>
+        <v>1375</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>16</v>
@@ -11402,25 +11267,25 @@
     </row>
     <row r="4" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>1352</v>
+        <v>1376</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>1353</v>
+        <v>1377</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>1354</v>
+        <v>1378</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>1355</v>
+        <v>1379</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>1349</v>
+        <v>1380</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>1356</v>
+        <v>1381</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>1357</v>
+        <v>1382</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>16</v>
@@ -11428,25 +11293,25 @@
     </row>
     <row r="5" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
-        <v>1358</v>
+        <v>1383</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>1359</v>
+        <v>1384</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>1360</v>
+        <v>1385</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>1361</v>
+        <v>1288</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>1349</v>
+        <v>1386</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>1362</v>
+        <v>1387</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>1363</v>
+        <v>1388</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>16</v>
@@ -11454,245 +11319,28 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>1364</v>
+        <v>1389</v>
       </c>
       <c r="B6" t="s">
-        <v>1365</v>
+        <v>1390</v>
       </c>
       <c r="C6" t="s">
-        <v>1366</v>
+        <v>1391</v>
       </c>
       <c r="D6" t="s">
-        <v>1367</v>
+        <v>1322</v>
       </c>
       <c r="E6" t="s">
-        <v>1368</v>
+        <v>1392</v>
       </c>
       <c r="F6" t="s">
-        <v>1369</v>
+        <v>1324</v>
       </c>
       <c r="G6" t="s">
-        <v>1370</v>
+        <v>1393</v>
       </c>
       <c r="H6" t="s">
-        <v>1371</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:H1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2600-000000000000}">
-  <dimension ref="A1:H8"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="18" customWidth="1"/>
-    <col min="2" max="2" width="26" customWidth="1"/>
-    <col min="3" max="3" width="30" customWidth="1"/>
-    <col min="4" max="4" width="26" customWidth="1"/>
-    <col min="5" max="5" width="34" customWidth="1"/>
-    <col min="6" max="6" width="26" customWidth="1"/>
-    <col min="7" max="7" width="36" customWidth="1"/>
-    <col min="8" max="8" width="10" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="5" t="s">
-        <v>1372</v>
-      </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-    </row>
-    <row r="2" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="2" t="s">
-        <v>1373</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>1374</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>1375</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>1376</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>1377</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>1378</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>1379</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>1380</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="2" t="s">
-        <v>1381</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>1382</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>1383</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>1384</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>1385</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>1386</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>1387</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="2" t="s">
-        <v>1388</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>1389</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>1390</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>1376</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>1391</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>1392</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>1393</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="2" t="s">
-        <v>1394</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>1395</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>1396</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>1397</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>1398</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>1113</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>1399</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="2" t="s">
-        <v>1400</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>1401</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>1402</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>1403</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>1404</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>1405</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>1406</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>1407</v>
-      </c>
-      <c r="B8" t="s">
-        <v>1408</v>
-      </c>
-      <c r="C8" t="s">
-        <v>1409</v>
-      </c>
-      <c r="D8" t="s">
-        <v>1367</v>
-      </c>
-      <c r="E8" t="s">
-        <v>1410</v>
-      </c>
-      <c r="F8" t="s">
-        <v>1369</v>
-      </c>
-      <c r="G8" t="s">
-        <v>1411</v>
-      </c>
-      <c r="H8" t="s">
-        <v>1371</v>
+        <v>1326</v>
       </c>
     </row>
   </sheetData>
@@ -11816,336 +11464,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2700-000000000000}">
-  <dimension ref="A1:H6"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="18" customWidth="1"/>
-    <col min="2" max="2" width="26" customWidth="1"/>
-    <col min="3" max="3" width="30" customWidth="1"/>
-    <col min="4" max="4" width="26" customWidth="1"/>
-    <col min="5" max="5" width="34" customWidth="1"/>
-    <col min="6" max="6" width="26" customWidth="1"/>
-    <col min="7" max="7" width="36" customWidth="1"/>
-    <col min="8" max="8" width="10" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="5" t="s">
-        <v>1412</v>
-      </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-    </row>
-    <row r="2" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="2" t="s">
-        <v>1413</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>1414</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>1415</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>1416</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>1417</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>1418</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>1419</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>1420</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="2" t="s">
-        <v>1421</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>1422</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>1423</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>1424</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>1425</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>1426</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>1427</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="2" t="s">
-        <v>1428</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>1429</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>1430</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>1431</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>1417</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>1432</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>1433</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>1434</v>
-      </c>
-      <c r="B6" t="s">
-        <v>1435</v>
-      </c>
-      <c r="C6" t="s">
-        <v>1436</v>
-      </c>
-      <c r="D6" t="s">
-        <v>1367</v>
-      </c>
-      <c r="E6" t="s">
-        <v>1437</v>
-      </c>
-      <c r="F6" t="s">
-        <v>1369</v>
-      </c>
-      <c r="G6" t="s">
-        <v>1438</v>
-      </c>
-      <c r="H6" t="s">
-        <v>1371</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:H1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2800-000000000000}">
-  <dimension ref="A1:H6"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="18" customWidth="1"/>
-    <col min="2" max="2" width="26" customWidth="1"/>
-    <col min="3" max="3" width="30" customWidth="1"/>
-    <col min="4" max="4" width="26" customWidth="1"/>
-    <col min="5" max="5" width="34" customWidth="1"/>
-    <col min="6" max="6" width="26" customWidth="1"/>
-    <col min="7" max="7" width="36" customWidth="1"/>
-    <col min="8" max="8" width="10" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="5" t="s">
-        <v>1439</v>
-      </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-    </row>
-    <row r="2" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="2" t="s">
-        <v>1440</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>1441</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>1442</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>1443</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>1444</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>1445</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>1446</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="2" t="s">
-        <v>1447</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>1448</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>1449</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>1450</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>1451</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>1452</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>1453</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="2" t="s">
-        <v>1454</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>1455</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>1456</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>1376</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>1457</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>1458</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>1459</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>1460</v>
-      </c>
-      <c r="B6" t="s">
-        <v>1461</v>
-      </c>
-      <c r="C6" t="s">
-        <v>1462</v>
-      </c>
-      <c r="D6" t="s">
-        <v>1367</v>
-      </c>
-      <c r="E6" t="s">
-        <v>1463</v>
-      </c>
-      <c r="F6" t="s">
-        <v>1369</v>
-      </c>
-      <c r="G6" t="s">
-        <v>1464</v>
-      </c>
-      <c r="H6" t="s">
-        <v>1371</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:H1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:H6"/>
